--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_chemical_basic.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_chemical_basic.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09097182194147843</v>
+        <v>0.09077814238662474</v>
       </c>
       <c r="C2">
-        <v>22148.77751079404</v>
+        <v>21991.81345134972</v>
       </c>
       <c r="D2">
-        <v>21941.67751079404</v>
+        <v>22014.40245134972</v>
       </c>
       <c r="E2">
-        <v>-3328.7</v>
+        <v>-3099.011</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>229.689</v>
       </c>
       <c r="G2">
         <v>207.1</v>
@@ -1439,28 +1439,28 @@
         <v>1868.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>11.5533567</v>
       </c>
       <c r="N2">
-        <v>1868.4</v>
+        <v>1856.8466433</v>
       </c>
       <c r="O2">
-        <v>467.1</v>
+        <v>464.211660825</v>
       </c>
       <c r="P2">
-        <v>1401.3</v>
+        <v>1392.634982475</v>
       </c>
       <c r="Q2">
-        <v>1944.6</v>
+        <v>1935.934982475</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09097182194147843</v>
+        <v>0.09131403271376237</v>
       </c>
       <c r="T2">
-        <v>0.9054086395470866</v>
+        <v>0.9122677959072918</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>161.7192343762744</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09077814238662474</v>
+        <v>0.09058446283177105</v>
       </c>
       <c r="C3">
-        <v>21991.81345134972</v>
+        <v>21835.33308374768</v>
       </c>
       <c r="D3">
-        <v>22014.40245134972</v>
+        <v>22087.61108374768</v>
       </c>
       <c r="E3">
-        <v>-3099.011</v>
+        <v>-2869.322</v>
       </c>
       <c r="F3">
-        <v>229.689</v>
+        <v>459.378</v>
       </c>
       <c r="G3">
         <v>207.1</v>
@@ -1521,28 +1521,28 @@
         <v>1868.4</v>
       </c>
       <c r="M3">
-        <v>11.5533567</v>
+        <v>23.1067134</v>
       </c>
       <c r="N3">
-        <v>1856.8466433</v>
+        <v>1845.2932866</v>
       </c>
       <c r="O3">
-        <v>464.211660825</v>
+        <v>461.32332165</v>
       </c>
       <c r="P3">
-        <v>1392.634982475</v>
+        <v>1383.96996495</v>
       </c>
       <c r="Q3">
-        <v>1935.934982475</v>
+        <v>1927.26996495</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09131403271376237</v>
+        <v>0.09166322737935821</v>
       </c>
       <c r="T3">
-        <v>0.9122677959072918</v>
+        <v>0.9192669350503584</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>161.7192343762744</v>
+        <v>80.85961718813719</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09058446283177105</v>
+        <v>0.09039078327691732</v>
       </c>
       <c r="C4">
-        <v>21835.33308374768</v>
+        <v>21679.34124962308</v>
       </c>
       <c r="D4">
-        <v>22087.61108374768</v>
+        <v>22161.30824962308</v>
       </c>
       <c r="E4">
-        <v>-2869.322</v>
+        <v>-2639.633</v>
       </c>
       <c r="F4">
-        <v>459.378</v>
+        <v>689.067</v>
       </c>
       <c r="G4">
         <v>207.1</v>
@@ -1603,28 +1603,28 @@
         <v>1868.4</v>
       </c>
       <c r="M4">
-        <v>23.1067134</v>
+        <v>34.6600701</v>
       </c>
       <c r="N4">
-        <v>1845.2932866</v>
+        <v>1833.7399299</v>
       </c>
       <c r="O4">
-        <v>461.32332165</v>
+        <v>458.434982475</v>
       </c>
       <c r="P4">
-        <v>1383.96996495</v>
+        <v>1375.304947425</v>
       </c>
       <c r="Q4">
-        <v>1927.26996495</v>
+        <v>1918.604947425</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09166322737935821</v>
+        <v>0.09201962193496632</v>
       </c>
       <c r="T4">
-        <v>0.9192669350503584</v>
+        <v>0.9264103863407045</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>80.85961718813719</v>
+        <v>53.90641145875814</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09039078327691732</v>
+        <v>0.09019710372206363</v>
       </c>
       <c r="C5">
-        <v>21679.34124962308</v>
+        <v>21523.84285544543</v>
       </c>
       <c r="D5">
-        <v>22161.30824962308</v>
+        <v>22235.49885544544</v>
       </c>
       <c r="E5">
-        <v>-2639.633</v>
+        <v>-2409.944</v>
       </c>
       <c r="F5">
-        <v>689.067</v>
+        <v>918.7560000000001</v>
       </c>
       <c r="G5">
         <v>207.1</v>
@@ -1685,28 +1685,28 @@
         <v>1868.4</v>
       </c>
       <c r="M5">
-        <v>34.6600701</v>
+        <v>46.2134268</v>
       </c>
       <c r="N5">
-        <v>1833.7399299</v>
+        <v>1822.1865732</v>
       </c>
       <c r="O5">
-        <v>458.434982475</v>
+        <v>455.5466433</v>
       </c>
       <c r="P5">
-        <v>1375.304947425</v>
+        <v>1366.6399299</v>
       </c>
       <c r="Q5">
-        <v>1918.604947425</v>
+        <v>1909.9399299</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09201962193496632</v>
+        <v>0.09238344137714963</v>
       </c>
       <c r="T5">
-        <v>0.9264103863407045</v>
+        <v>0.9337026595329331</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>53.90641145875814</v>
+        <v>40.4298085940686</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09019710372206363</v>
+        <v>0.09000342416720995</v>
       </c>
       <c r="C6">
-        <v>21523.84285544543</v>
+        <v>21368.8428736076</v>
       </c>
       <c r="D6">
-        <v>22235.49885544544</v>
+        <v>22310.1878736076</v>
       </c>
       <c r="E6">
-        <v>-2409.944</v>
+        <v>-2180.255</v>
       </c>
       <c r="F6">
-        <v>918.7560000000001</v>
+        <v>1148.445</v>
       </c>
       <c r="G6">
         <v>207.1</v>
@@ -1767,28 +1767,28 @@
         <v>1868.4</v>
       </c>
       <c r="M6">
-        <v>46.2134268</v>
+        <v>57.7667835</v>
       </c>
       <c r="N6">
-        <v>1822.1865732</v>
+        <v>1810.6332165</v>
       </c>
       <c r="O6">
-        <v>455.5466433</v>
+        <v>452.658304125</v>
       </c>
       <c r="P6">
-        <v>1366.6399299</v>
+        <v>1357.974912375</v>
       </c>
       <c r="Q6">
-        <v>1909.9399299</v>
+        <v>1901.274912375</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09238344137714963</v>
+        <v>0.09275492017601047</v>
       </c>
       <c r="T6">
-        <v>0.9337026595329331</v>
+        <v>0.9411484542660505</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>40.4298085940686</v>
+        <v>32.34384687525488</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09000342416720995</v>
+        <v>0.08980974461235625</v>
       </c>
       <c r="C7">
-        <v>21368.8428736076</v>
+        <v>21214.34634353665</v>
       </c>
       <c r="D7">
-        <v>22310.1878736076</v>
+        <v>22385.38034353665</v>
       </c>
       <c r="E7">
-        <v>-2180.255</v>
+        <v>-1950.566</v>
       </c>
       <c r="F7">
-        <v>1148.445</v>
+        <v>1378.134</v>
       </c>
       <c r="G7">
         <v>207.1</v>
@@ -1849,28 +1849,28 @@
         <v>1868.4</v>
       </c>
       <c r="M7">
-        <v>57.7667835</v>
+        <v>69.32014020000001</v>
       </c>
       <c r="N7">
-        <v>1810.6332165</v>
+        <v>1799.0798598</v>
       </c>
       <c r="O7">
-        <v>452.658304125</v>
+        <v>449.76996495</v>
       </c>
       <c r="P7">
-        <v>1357.974912375</v>
+        <v>1349.30989485</v>
       </c>
       <c r="Q7">
-        <v>1901.274912375</v>
+        <v>1892.60989485</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09275492017601047</v>
+        <v>0.0931343027791024</v>
       </c>
       <c r="T7">
-        <v>0.9411484542660505</v>
+        <v>0.9487526701637025</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>32.34384687525488</v>
+        <v>26.95320572937906</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08980974461235625</v>
+        <v>0.08961606505750257</v>
       </c>
       <c r="C8">
-        <v>21214.34634353665</v>
+        <v>21060.35837282731</v>
       </c>
       <c r="D8">
-        <v>22385.38034353665</v>
+        <v>22461.08137282731</v>
       </c>
       <c r="E8">
-        <v>-1950.566</v>
+        <v>-1720.877</v>
       </c>
       <c r="F8">
-        <v>1378.134</v>
+        <v>1607.823</v>
       </c>
       <c r="G8">
         <v>207.1</v>
@@ -1931,28 +1931,28 @@
         <v>1868.4</v>
       </c>
       <c r="M8">
-        <v>69.3201402</v>
+        <v>80.87349689999999</v>
       </c>
       <c r="N8">
-        <v>1799.0798598</v>
+        <v>1787.5265031</v>
       </c>
       <c r="O8">
-        <v>449.76996495</v>
+        <v>446.881625775</v>
       </c>
       <c r="P8">
-        <v>1349.30989485</v>
+        <v>1340.644877325</v>
       </c>
       <c r="Q8">
-        <v>1892.60989485</v>
+        <v>1883.944877325</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0931343027791024</v>
+        <v>0.09352184414785222</v>
       </c>
       <c r="T8">
-        <v>0.9487526701637025</v>
+        <v>0.956520417586035</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>26.95320572937907</v>
+        <v>23.1027477680392</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08961606505750255</v>
+        <v>0.08942238550264889</v>
       </c>
       <c r="C9">
-        <v>21060.35837282732</v>
+        <v>20906.88413839853</v>
       </c>
       <c r="D9">
-        <v>22461.08137282732</v>
+        <v>22537.29613839853</v>
       </c>
       <c r="E9">
-        <v>-1720.876999999999</v>
+        <v>-1491.188</v>
       </c>
       <c r="F9">
-        <v>1607.823</v>
+        <v>1837.512</v>
       </c>
       <c r="G9">
         <v>207.1</v>
@@ -2013,28 +2013,28 @@
         <v>1868.4</v>
       </c>
       <c r="M9">
-        <v>80.87349690000001</v>
+        <v>92.4268536</v>
       </c>
       <c r="N9">
-        <v>1787.5265031</v>
+        <v>1775.9731464</v>
       </c>
       <c r="O9">
-        <v>446.881625775</v>
+        <v>443.9932866</v>
       </c>
       <c r="P9">
-        <v>1340.644877325</v>
+        <v>1331.9798598</v>
       </c>
       <c r="Q9">
-        <v>1883.944877325</v>
+        <v>1875.2798598</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09352184414785222</v>
+        <v>0.09391781032896616</v>
       </c>
       <c r="T9">
-        <v>0.956520417586035</v>
+        <v>0.9644570290827662</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>23.1027477680392</v>
+        <v>20.2149042970343</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08942238550264889</v>
+        <v>0.08922870594779518</v>
       </c>
       <c r="C10">
-        <v>20906.88413839853</v>
+        <v>20753.92888767361</v>
       </c>
       <c r="D10">
-        <v>22537.29613839853</v>
+        <v>22614.02988767362</v>
       </c>
       <c r="E10">
-        <v>-1491.188</v>
+        <v>-1261.499</v>
       </c>
       <c r="F10">
-        <v>1837.512</v>
+        <v>2067.201</v>
       </c>
       <c r="G10">
         <v>207.1</v>
@@ -2095,28 +2095,28 @@
         <v>1868.4</v>
       </c>
       <c r="M10">
-        <v>92.4268536</v>
+        <v>103.9802103</v>
       </c>
       <c r="N10">
-        <v>1775.9731464</v>
+        <v>1764.4197897</v>
       </c>
       <c r="O10">
-        <v>443.9932866</v>
+        <v>441.104947425</v>
       </c>
       <c r="P10">
-        <v>1331.9798598</v>
+        <v>1323.314842275</v>
       </c>
       <c r="Q10">
-        <v>1875.2798598</v>
+        <v>1866.614842275</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09391781032896616</v>
+        <v>0.09432247906351118</v>
       </c>
       <c r="T10">
-        <v>0.9644570290827662</v>
+        <v>0.9725680716014035</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>20.2149042970343</v>
+        <v>17.96880381958605</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08922870594779518</v>
+        <v>0.08903502639294147</v>
       </c>
       <c r="C11">
-        <v>20753.92888767361</v>
+        <v>20601.49793978456</v>
       </c>
       <c r="D11">
-        <v>22614.02988767362</v>
+        <v>22691.28793978456</v>
       </c>
       <c r="E11">
-        <v>-1261.499</v>
+        <v>-1031.81</v>
       </c>
       <c r="F11">
-        <v>2067.201</v>
+        <v>2296.89</v>
       </c>
       <c r="G11">
         <v>207.1</v>
@@ -2177,28 +2177,28 @@
         <v>1868.4</v>
       </c>
       <c r="M11">
-        <v>103.9802103</v>
+        <v>115.533567</v>
       </c>
       <c r="N11">
-        <v>1764.4197897</v>
+        <v>1752.866433</v>
       </c>
       <c r="O11">
-        <v>441.104947425</v>
+        <v>438.21660825</v>
       </c>
       <c r="P11">
-        <v>1323.314842275</v>
+        <v>1314.64982475</v>
       </c>
       <c r="Q11">
-        <v>1866.614842275</v>
+        <v>1857.94982475</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09432247906351118</v>
+        <v>0.09473614043660164</v>
       </c>
       <c r="T11">
-        <v>0.9725680716014035</v>
+        <v>0.9808593595093438</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.96880381958605</v>
+        <v>16.17192343762744</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08903502639294147</v>
+        <v>0.08884134683808777</v>
       </c>
       <c r="C12">
-        <v>20601.49793978456</v>
+        <v>20449.59668680119</v>
       </c>
       <c r="D12">
-        <v>22691.28793978456</v>
+        <v>22769.07568680119</v>
       </c>
       <c r="E12">
-        <v>-1031.809999999999</v>
+        <v>-802.1209999999996</v>
       </c>
       <c r="F12">
-        <v>2296.89</v>
+        <v>2526.579</v>
       </c>
       <c r="G12">
         <v>207.1</v>
@@ -2259,28 +2259,28 @@
         <v>1868.4</v>
       </c>
       <c r="M12">
-        <v>115.533567</v>
+        <v>127.0869237</v>
       </c>
       <c r="N12">
-        <v>1752.866433</v>
+        <v>1741.3130763</v>
       </c>
       <c r="O12">
-        <v>438.21660825</v>
+        <v>435.328269075</v>
       </c>
       <c r="P12">
-        <v>1314.64982475</v>
+        <v>1305.984807225</v>
       </c>
       <c r="Q12">
-        <v>1857.94982475</v>
+        <v>1849.284807225</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09473614043660164</v>
+        <v>0.09515909757088514</v>
       </c>
       <c r="T12">
-        <v>0.9808593595093438</v>
+        <v>0.9893369684938672</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.17192343762744</v>
+        <v>14.70174857966131</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08884134683808777</v>
+        <v>0.08864766728323407</v>
       </c>
       <c r="C13">
-        <v>20449.59668680119</v>
+        <v>20298.23059498565</v>
       </c>
       <c r="D13">
-        <v>22769.07568680119</v>
+        <v>22847.39859498565</v>
       </c>
       <c r="E13">
-        <v>-802.1209999999996</v>
+        <v>-572.4319999999998</v>
       </c>
       <c r="F13">
-        <v>2526.579</v>
+        <v>2756.268</v>
       </c>
       <c r="G13">
         <v>207.1</v>
@@ -2341,28 +2341,28 @@
         <v>1868.4</v>
       </c>
       <c r="M13">
-        <v>127.0869237</v>
+        <v>138.6402804</v>
       </c>
       <c r="N13">
-        <v>1741.3130763</v>
+        <v>1729.7597196</v>
       </c>
       <c r="O13">
-        <v>435.328269075</v>
+        <v>432.4399299</v>
       </c>
       <c r="P13">
-        <v>1305.984807225</v>
+        <v>1297.3197897</v>
       </c>
       <c r="Q13">
-        <v>1849.284807225</v>
+        <v>1840.6197897</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09515909757088514</v>
+        <v>0.09559166736731145</v>
       </c>
       <c r="T13">
-        <v>0.9893369684938672</v>
+        <v>0.9980072504098568</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.70174857966131</v>
+        <v>13.47660286468953</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08864766728323407</v>
+        <v>0.0884539877283804</v>
       </c>
       <c r="C14">
-        <v>20298.23059498565</v>
+        <v>20147.40520607284</v>
       </c>
       <c r="D14">
-        <v>22847.39859498565</v>
+        <v>22926.26220607284</v>
       </c>
       <c r="E14">
-        <v>-572.4319999999998</v>
+        <v>-342.7429999999995</v>
       </c>
       <c r="F14">
-        <v>2756.268</v>
+        <v>2985.957</v>
       </c>
       <c r="G14">
         <v>207.1</v>
@@ -2423,28 +2423,28 @@
         <v>1868.4</v>
       </c>
       <c r="M14">
-        <v>138.6402804</v>
+        <v>150.1936371</v>
       </c>
       <c r="N14">
-        <v>1729.7597196</v>
+        <v>1718.2063629</v>
       </c>
       <c r="O14">
-        <v>432.4399299</v>
+        <v>429.551590725</v>
       </c>
       <c r="P14">
-        <v>1297.3197897</v>
+        <v>1288.654772175</v>
       </c>
       <c r="Q14">
-        <v>1840.6197897</v>
+        <v>1831.954772175</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09559166736731145</v>
+        <v>0.09603418129698896</v>
       </c>
       <c r="T14">
-        <v>0.9980072504098568</v>
+        <v>1.006876849151501</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>13.47660286468953</v>
+        <v>12.43994110586726</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0884539877283804</v>
+        <v>0.08826030817352667</v>
       </c>
       <c r="C15">
-        <v>20147.40520607284</v>
+        <v>19997.12613857758</v>
       </c>
       <c r="D15">
-        <v>22926.26220607284</v>
+        <v>23005.67213857759</v>
       </c>
       <c r="E15">
-        <v>-342.7429999999995</v>
+        <v>-113.0539999999992</v>
       </c>
       <c r="F15">
-        <v>2985.957</v>
+        <v>3215.646000000001</v>
       </c>
       <c r="G15">
         <v>207.1</v>
@@ -2505,28 +2505,28 @@
         <v>1868.4</v>
       </c>
       <c r="M15">
-        <v>150.1936371</v>
+        <v>161.7469938</v>
       </c>
       <c r="N15">
-        <v>1718.2063629</v>
+        <v>1706.6530062</v>
       </c>
       <c r="O15">
-        <v>429.551590725</v>
+        <v>426.66325155</v>
       </c>
       <c r="P15">
-        <v>1288.654772175</v>
+        <v>1279.98975465</v>
       </c>
       <c r="Q15">
-        <v>1831.954772175</v>
+        <v>1823.28975465</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09603418129698896</v>
+        <v>0.09648698624828685</v>
       </c>
       <c r="T15">
-        <v>1.006876849151501</v>
+        <v>1.015952717631324</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>12.43994110586726</v>
+        <v>11.5513738840196</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08826030817352667</v>
+        <v>0.088066628618673</v>
       </c>
       <c r="C16">
-        <v>19997.12613857758</v>
+        <v>19847.39908912881</v>
       </c>
       <c r="D16">
-        <v>23005.67213857759</v>
+        <v>23085.63408912881</v>
       </c>
       <c r="E16">
-        <v>-113.0539999999992</v>
+        <v>116.6350000000011</v>
       </c>
       <c r="F16">
-        <v>3215.646000000001</v>
+        <v>3445.335000000001</v>
       </c>
       <c r="G16">
         <v>207.1</v>
@@ -2587,28 +2587,28 @@
         <v>1868.4</v>
       </c>
       <c r="M16">
-        <v>161.7469938</v>
+        <v>173.3003505</v>
       </c>
       <c r="N16">
-        <v>1706.6530062</v>
+        <v>1695.0996495</v>
       </c>
       <c r="O16">
-        <v>426.66325155</v>
+        <v>423.774912375</v>
       </c>
       <c r="P16">
-        <v>1279.98975465</v>
+        <v>1271.324737125</v>
       </c>
       <c r="Q16">
-        <v>1823.28975465</v>
+        <v>1814.624737125</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09648698624828685</v>
+        <v>0.09695044543373293</v>
       </c>
       <c r="T16">
-        <v>1.015952717631324</v>
+        <v>1.02524213595773</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.5513738840196</v>
+        <v>10.78128229175162</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.088066628618673</v>
+        <v>0.08787294906381929</v>
       </c>
       <c r="C17">
-        <v>19847.39908912881</v>
+        <v>19698.22983383199</v>
       </c>
       <c r="D17">
-        <v>23085.63408912881</v>
+        <v>23166.15383383199</v>
       </c>
       <c r="E17">
-        <v>116.6350000000002</v>
+        <v>346.3240000000005</v>
       </c>
       <c r="F17">
-        <v>3445.335</v>
+        <v>3675.024</v>
       </c>
       <c r="G17">
         <v>207.1</v>
@@ -2669,28 +2669,28 @@
         <v>1868.4</v>
       </c>
       <c r="M17">
-        <v>173.3003505</v>
+        <v>184.8537072</v>
       </c>
       <c r="N17">
-        <v>1695.0996495</v>
+        <v>1683.5462928</v>
       </c>
       <c r="O17">
-        <v>423.774912375</v>
+        <v>420.8865732</v>
       </c>
       <c r="P17">
-        <v>1271.324737125</v>
+        <v>1262.6597196</v>
       </c>
       <c r="Q17">
-        <v>1814.624737125</v>
+        <v>1805.9597196</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09695044543373293</v>
+        <v>0.09742493936168964</v>
       </c>
       <c r="T17">
-        <v>1.02524213595773</v>
+        <v>1.034752730910956</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.78128229175163</v>
+        <v>10.10745214851715</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08787294906381929</v>
+        <v>0.0876792695089656</v>
       </c>
       <c r="C18">
-        <v>19698.22983383199</v>
+        <v>19549.62422965986</v>
       </c>
       <c r="D18">
-        <v>23166.15383383199</v>
+        <v>23247.23722965986</v>
       </c>
       <c r="E18">
-        <v>346.3240000000005</v>
+        <v>576.0130000000008</v>
       </c>
       <c r="F18">
-        <v>3675.024</v>
+        <v>3904.713000000001</v>
       </c>
       <c r="G18">
         <v>207.1</v>
@@ -2751,28 +2751,28 @@
         <v>1868.4</v>
       </c>
       <c r="M18">
-        <v>184.8537072</v>
+        <v>196.4070639</v>
       </c>
       <c r="N18">
-        <v>1683.5462928</v>
+        <v>1671.9929361</v>
       </c>
       <c r="O18">
-        <v>420.8865732</v>
+        <v>417.998234025</v>
       </c>
       <c r="P18">
-        <v>1262.6597196</v>
+        <v>1253.994702075</v>
       </c>
       <c r="Q18">
-        <v>1805.9597196</v>
+        <v>1797.294702075</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09742493936168964</v>
+        <v>0.09791086687827182</v>
       </c>
       <c r="T18">
-        <v>1.034752730910956</v>
+        <v>1.04449249682691</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.10745214851715</v>
+        <v>9.512896139780844</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0876792695089656</v>
+        <v>0.08748558995411192</v>
       </c>
       <c r="C19">
-        <v>19549.62422965986</v>
+        <v>19401.5882158727</v>
       </c>
       <c r="D19">
-        <v>23247.23722965986</v>
+        <v>23328.89021587271</v>
       </c>
       <c r="E19">
-        <v>576.0130000000008</v>
+        <v>805.7020000000011</v>
       </c>
       <c r="F19">
-        <v>3904.713000000001</v>
+        <v>4134.402000000001</v>
       </c>
       <c r="G19">
         <v>207.1</v>
@@ -2833,28 +2833,28 @@
         <v>1868.4</v>
       </c>
       <c r="M19">
-        <v>196.4070639</v>
+        <v>207.9604206</v>
       </c>
       <c r="N19">
-        <v>1671.9929361</v>
+        <v>1660.4395794</v>
       </c>
       <c r="O19">
-        <v>417.998234025</v>
+        <v>415.10989485</v>
       </c>
       <c r="P19">
-        <v>1253.994702075</v>
+        <v>1245.32968455</v>
       </c>
       <c r="Q19">
-        <v>1797.294702075</v>
+        <v>1788.62968455</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09791086687827182</v>
+        <v>0.09840864628550233</v>
       </c>
       <c r="T19">
-        <v>1.04449249682691</v>
+        <v>1.054469818009107</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.512896139780844</v>
+        <v>8.98440190979302</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08748558995411192</v>
+        <v>0.08750566039925822</v>
       </c>
       <c r="C20">
-        <v>19401.5882158727</v>
+        <v>19163.41112566383</v>
       </c>
       <c r="D20">
-        <v>23328.89021587271</v>
+        <v>23320.40212566383</v>
       </c>
       <c r="E20">
-        <v>805.7020000000002</v>
+        <v>1035.391000000001</v>
       </c>
       <c r="F20">
-        <v>4134.402</v>
+        <v>4364.091</v>
       </c>
       <c r="G20">
         <v>207.1</v>
@@ -2915,45 +2915,45 @@
         <v>1868.4</v>
       </c>
       <c r="M20">
-        <v>207.9604206</v>
+        <v>226.0599138</v>
       </c>
       <c r="N20">
-        <v>1660.4395794</v>
+        <v>1642.3400862</v>
       </c>
       <c r="O20">
-        <v>415.10989485</v>
+        <v>410.58502155</v>
       </c>
       <c r="P20">
-        <v>1245.32968455</v>
+        <v>1231.75506465</v>
       </c>
       <c r="Q20">
-        <v>1788.62968455</v>
+        <v>1775.05506465</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09840864628550233</v>
+        <v>0.09891871654229409</v>
       </c>
       <c r="T20">
-        <v>1.054469818009107</v>
+        <v>1.064693492800741</v>
       </c>
       <c r="U20">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>8.984401909793021</v>
+        <v>8.265065524412316</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08750566039925822</v>
+        <v>0.08732323084440452</v>
       </c>
       <c r="C21">
-        <v>19163.41112566383</v>
+        <v>19011.10213779364</v>
       </c>
       <c r="D21">
-        <v>23320.40212566383</v>
+        <v>23397.78213779364</v>
       </c>
       <c r="E21">
-        <v>1035.391000000001</v>
+        <v>1265.080000000001</v>
       </c>
       <c r="F21">
-        <v>4364.091</v>
+        <v>4593.780000000001</v>
       </c>
       <c r="G21">
         <v>207.1</v>
@@ -2997,28 +2997,28 @@
         <v>1868.4</v>
       </c>
       <c r="M21">
-        <v>226.0599138</v>
+        <v>237.957804</v>
       </c>
       <c r="N21">
-        <v>1642.3400862</v>
+        <v>1630.442196</v>
       </c>
       <c r="O21">
-        <v>410.58502155</v>
+        <v>407.610549</v>
       </c>
       <c r="P21">
-        <v>1231.75506465</v>
+        <v>1222.831647</v>
       </c>
       <c r="Q21">
-        <v>1775.05506465</v>
+        <v>1766.131647</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09891871654229409</v>
+        <v>0.09944153855550564</v>
       </c>
       <c r="T21">
-        <v>1.064693492800741</v>
+        <v>1.075172759462165</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.265065524412316</v>
+        <v>7.851812248191699</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08732323084440452</v>
+        <v>0.08714080128955082</v>
       </c>
       <c r="C22">
-        <v>19011.10213779364</v>
+        <v>18859.30837262108</v>
       </c>
       <c r="D22">
-        <v>23397.78213779364</v>
+        <v>23475.67737262108</v>
       </c>
       <c r="E22">
-        <v>1265.080000000001</v>
+        <v>1494.769000000001</v>
       </c>
       <c r="F22">
-        <v>4593.780000000001</v>
+        <v>4823.469000000001</v>
       </c>
       <c r="G22">
         <v>207.1</v>
@@ -3079,28 +3079,28 @@
         <v>1868.4</v>
       </c>
       <c r="M22">
-        <v>237.957804</v>
+        <v>249.8556942</v>
       </c>
       <c r="N22">
-        <v>1630.442196</v>
+        <v>1618.5443058</v>
       </c>
       <c r="O22">
-        <v>407.610549</v>
+        <v>404.63607645</v>
       </c>
       <c r="P22">
-        <v>1222.831647</v>
+        <v>1213.90822935</v>
       </c>
       <c r="Q22">
-        <v>1766.131647</v>
+        <v>1757.20822935</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09944153855550564</v>
+        <v>0.09997759656905167</v>
       </c>
       <c r="T22">
-        <v>1.075172759462165</v>
+        <v>1.085917324013753</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.851812248191699</v>
+        <v>7.477916426849237</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08714080128955082</v>
+        <v>0.08695837173469712</v>
       </c>
       <c r="C23">
-        <v>18859.30837262108</v>
+        <v>18708.03499312912</v>
       </c>
       <c r="D23">
-        <v>23475.67737262108</v>
+        <v>23554.09299312912</v>
       </c>
       <c r="E23">
-        <v>1494.769</v>
+        <v>1724.458000000001</v>
       </c>
       <c r="F23">
-        <v>4823.469</v>
+        <v>5053.158</v>
       </c>
       <c r="G23">
         <v>207.1</v>
@@ -3161,28 +3161,28 @@
         <v>1868.4</v>
       </c>
       <c r="M23">
-        <v>249.8556942</v>
+        <v>261.7535844</v>
       </c>
       <c r="N23">
-        <v>1618.5443058</v>
+        <v>1606.6464156</v>
       </c>
       <c r="O23">
-        <v>404.63607645</v>
+        <v>401.6616039</v>
       </c>
       <c r="P23">
-        <v>1213.90822935</v>
+        <v>1204.9848117</v>
       </c>
       <c r="Q23">
-        <v>1757.20822935</v>
+        <v>1748.2848117</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09997759656905167</v>
+        <v>0.1005273996598681</v>
       </c>
       <c r="T23">
-        <v>1.085917324013753</v>
+        <v>1.096937390220509</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.477916426849239</v>
+        <v>7.138011134719727</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08695837173469712</v>
+        <v>0.08677594217984343</v>
       </c>
       <c r="C24">
-        <v>18708.03499312912</v>
+        <v>18557.28723151542</v>
       </c>
       <c r="D24">
-        <v>23554.09299312912</v>
+        <v>23633.03423151542</v>
       </c>
       <c r="E24">
-        <v>1724.458000000001</v>
+        <v>1954.147000000001</v>
       </c>
       <c r="F24">
-        <v>5053.158</v>
+        <v>5282.847000000001</v>
       </c>
       <c r="G24">
         <v>207.1</v>
@@ -3243,28 +3243,28 @@
         <v>1868.4</v>
       </c>
       <c r="M24">
-        <v>261.7535844</v>
+        <v>273.6514746</v>
       </c>
       <c r="N24">
-        <v>1606.6464156</v>
+        <v>1594.7485254</v>
       </c>
       <c r="O24">
-        <v>401.6616039</v>
+        <v>398.68713135</v>
       </c>
       <c r="P24">
-        <v>1204.9848117</v>
+        <v>1196.06139405</v>
       </c>
       <c r="Q24">
-        <v>1748.2848117</v>
+        <v>1739.36139405</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1005273996598681</v>
+        <v>0.101091483350446</v>
       </c>
       <c r="T24">
-        <v>1.096937390220509</v>
+        <v>1.108243691913155</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.138011134719727</v>
+        <v>6.827662824514522</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08677594217984343</v>
+        <v>0.08689951262498972</v>
       </c>
       <c r="C25">
-        <v>18557.28723151542</v>
+        <v>18274.06892157223</v>
       </c>
       <c r="D25">
-        <v>23633.03423151542</v>
+        <v>23579.50492157223</v>
       </c>
       <c r="E25">
-        <v>1954.147000000001</v>
+        <v>2183.836000000001</v>
       </c>
       <c r="F25">
-        <v>5282.847000000001</v>
+        <v>5512.536000000001</v>
       </c>
       <c r="G25">
         <v>207.1</v>
@@ -3325,45 +3325,45 @@
         <v>1868.4</v>
       </c>
       <c r="M25">
-        <v>273.6514746</v>
+        <v>294.9206760000001</v>
       </c>
       <c r="N25">
-        <v>1594.7485254</v>
+        <v>1573.479324</v>
       </c>
       <c r="O25">
-        <v>398.68713135</v>
+        <v>393.369831</v>
       </c>
       <c r="P25">
-        <v>1196.06139405</v>
+        <v>1180.109493</v>
       </c>
       <c r="Q25">
-        <v>1739.36139405</v>
+        <v>1723.409493</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.101091483350446</v>
+        <v>0.1016704113486707</v>
       </c>
       <c r="T25">
-        <v>1.108243691913155</v>
+        <v>1.11984752786087</v>
       </c>
       <c r="U25">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>6.827662824514522</v>
+        <v>6.335262841998909</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08689951262498972</v>
+        <v>0.08672983307013604</v>
       </c>
       <c r="C26">
-        <v>18274.06892157223</v>
+        <v>18117.94548946171</v>
       </c>
       <c r="D26">
-        <v>23579.50492157223</v>
+        <v>23653.07048946171</v>
       </c>
       <c r="E26">
-        <v>2183.836</v>
+        <v>2413.525000000001</v>
       </c>
       <c r="F26">
-        <v>5512.536</v>
+        <v>5742.225</v>
       </c>
       <c r="G26">
         <v>207.1</v>
@@ -3407,28 +3407,28 @@
         <v>1868.4</v>
       </c>
       <c r="M26">
-        <v>294.920676</v>
+        <v>307.2090375</v>
       </c>
       <c r="N26">
-        <v>1573.479324</v>
+        <v>1561.1909625</v>
       </c>
       <c r="O26">
-        <v>393.369831</v>
+        <v>390.297740625</v>
       </c>
       <c r="P26">
-        <v>1180.109493</v>
+        <v>1170.893221875</v>
       </c>
       <c r="Q26">
-        <v>1723.409493</v>
+        <v>1714.193221875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1016704113486707</v>
+        <v>0.102264777426848</v>
       </c>
       <c r="T26">
-        <v>1.11984752786087</v>
+        <v>1.131760799433858</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.335262841998911</v>
+        <v>6.081852328318955</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08672983307013604</v>
+        <v>0.08656015351528235</v>
       </c>
       <c r="C27">
-        <v>18117.94548946171</v>
+        <v>17962.28252759214</v>
       </c>
       <c r="D27">
-        <v>23653.07048946171</v>
+        <v>23727.09652759214</v>
       </c>
       <c r="E27">
-        <v>2413.525000000001</v>
+        <v>2643.214000000001</v>
       </c>
       <c r="F27">
-        <v>5742.225</v>
+        <v>5971.914000000001</v>
       </c>
       <c r="G27">
         <v>207.1</v>
@@ -3489,28 +3489,28 @@
         <v>1868.4</v>
       </c>
       <c r="M27">
-        <v>307.2090375</v>
+        <v>319.497399</v>
       </c>
       <c r="N27">
-        <v>1561.1909625</v>
+        <v>1548.902601</v>
       </c>
       <c r="O27">
-        <v>390.297740625</v>
+        <v>387.22565025</v>
       </c>
       <c r="P27">
-        <v>1170.893221875</v>
+        <v>1161.67695075</v>
       </c>
       <c r="Q27">
-        <v>1714.193221875</v>
+        <v>1704.97695075</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.102264777426848</v>
+        <v>0.1028752074530842</v>
       </c>
       <c r="T27">
-        <v>1.131760799433858</v>
+        <v>1.14399605131963</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.081852328318955</v>
+        <v>5.847934931075917</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08656015351528235</v>
+        <v>0.08639047396042865</v>
       </c>
       <c r="C28">
-        <v>17962.28252759214</v>
+        <v>17807.08437288069</v>
       </c>
       <c r="D28">
-        <v>23727.09652759214</v>
+        <v>23801.58737288069</v>
       </c>
       <c r="E28">
-        <v>2643.214000000001</v>
+        <v>2872.903000000001</v>
       </c>
       <c r="F28">
-        <v>5971.914000000001</v>
+        <v>6201.603000000001</v>
       </c>
       <c r="G28">
         <v>207.1</v>
@@ -3571,28 +3571,28 @@
         <v>1868.4</v>
       </c>
       <c r="M28">
-        <v>319.497399</v>
+        <v>331.7857605</v>
       </c>
       <c r="N28">
-        <v>1548.902601</v>
+        <v>1536.6142395</v>
       </c>
       <c r="O28">
-        <v>387.22565025</v>
+        <v>384.153559875</v>
       </c>
       <c r="P28">
-        <v>1161.67695075</v>
+        <v>1152.460679625</v>
       </c>
       <c r="Q28">
-        <v>1704.97695075</v>
+        <v>1695.760679625</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1028752074530842</v>
+        <v>0.1035023615896283</v>
       </c>
       <c r="T28">
-        <v>1.14399605131963</v>
+        <v>1.156566515585833</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.847934931075917</v>
+        <v>5.631344748443476</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08639047396042865</v>
+        <v>0.08638879440557495</v>
       </c>
       <c r="C29">
-        <v>17807.08437288069</v>
+        <v>17578.13505036628</v>
       </c>
       <c r="D29">
-        <v>23801.58737288069</v>
+        <v>23802.32705036628</v>
       </c>
       <c r="E29">
-        <v>2872.903000000001</v>
+        <v>3102.592000000001</v>
       </c>
       <c r="F29">
-        <v>6201.603000000001</v>
+        <v>6431.292000000001</v>
       </c>
       <c r="G29">
         <v>207.1</v>
@@ -3653,45 +3653,45 @@
         <v>1868.4</v>
       </c>
       <c r="M29">
-        <v>331.7857605</v>
+        <v>349.2191556000001</v>
       </c>
       <c r="N29">
-        <v>1536.6142395</v>
+        <v>1519.1808444</v>
       </c>
       <c r="O29">
-        <v>384.153559875</v>
+        <v>379.7952111</v>
       </c>
       <c r="P29">
-        <v>1152.460679625</v>
+        <v>1139.3856333</v>
       </c>
       <c r="Q29">
-        <v>1695.760679625</v>
+        <v>1682.6856333</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1035023615896283</v>
+        <v>0.1041469366744097</v>
       </c>
       <c r="T29">
-        <v>1.156566515585833</v>
+        <v>1.169486159414987</v>
       </c>
       <c r="U29">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>5.631344748443476</v>
+        <v>5.350221973905946</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08638879440557495</v>
+        <v>0.08622511485072124</v>
       </c>
       <c r="C30">
-        <v>17578.13505036628</v>
+        <v>17420.75189826655</v>
       </c>
       <c r="D30">
-        <v>23802.32705036628</v>
+        <v>23874.63289826655</v>
       </c>
       <c r="E30">
-        <v>3102.592000000001</v>
+        <v>3332.281000000002</v>
       </c>
       <c r="F30">
-        <v>6431.292000000001</v>
+        <v>6660.981000000002</v>
       </c>
       <c r="G30">
         <v>207.1</v>
@@ -3735,28 +3735,28 @@
         <v>1868.4</v>
       </c>
       <c r="M30">
-        <v>349.2191556000001</v>
+        <v>361.6912683000001</v>
       </c>
       <c r="N30">
-        <v>1519.1808444</v>
+        <v>1506.7087317</v>
       </c>
       <c r="O30">
-        <v>379.7952111</v>
+        <v>376.677182925</v>
       </c>
       <c r="P30">
-        <v>1139.3856333</v>
+        <v>1130.031548775</v>
       </c>
       <c r="Q30">
-        <v>1682.6856333</v>
+        <v>1673.331548775</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1041469366744097</v>
+        <v>0.1048096688038327</v>
       </c>
       <c r="T30">
-        <v>1.169486159414987</v>
+        <v>1.182769736873131</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.350221973905946</v>
+        <v>5.165731561012637</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08622511485072124</v>
+        <v>0.08606143529586754</v>
       </c>
       <c r="C31">
-        <v>17420.75189826655</v>
+        <v>17263.8093808882</v>
       </c>
       <c r="D31">
-        <v>23874.63289826655</v>
+        <v>23947.3793808882</v>
       </c>
       <c r="E31">
-        <v>3332.281</v>
+        <v>3561.97</v>
       </c>
       <c r="F31">
-        <v>6660.981</v>
+        <v>6890.67</v>
       </c>
       <c r="G31">
         <v>207.1</v>
@@ -3817,28 +3817,28 @@
         <v>1868.4</v>
       </c>
       <c r="M31">
-        <v>361.6912683</v>
+        <v>374.163381</v>
       </c>
       <c r="N31">
-        <v>1506.7087317</v>
+        <v>1494.236619</v>
       </c>
       <c r="O31">
-        <v>376.677182925</v>
+        <v>373.55915475</v>
       </c>
       <c r="P31">
-        <v>1130.031548775</v>
+        <v>1120.67746425</v>
       </c>
       <c r="Q31">
-        <v>1673.331548775</v>
+        <v>1663.97746425</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1048096688038327</v>
+        <v>0.1054913361369536</v>
       </c>
       <c r="T31">
-        <v>1.182769736873131</v>
+        <v>1.196432845115793</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.165731561012638</v>
+        <v>4.993540508978883</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08606143529586754</v>
+        <v>0.08589775574101385</v>
       </c>
       <c r="C32">
-        <v>17263.8093808882</v>
+        <v>17107.31153841009</v>
       </c>
       <c r="D32">
-        <v>23947.3793808882</v>
+        <v>24020.57053841009</v>
       </c>
       <c r="E32">
-        <v>3561.97</v>
+        <v>3791.659000000001</v>
       </c>
       <c r="F32">
-        <v>6890.67</v>
+        <v>7120.359</v>
       </c>
       <c r="G32">
         <v>207.1</v>
@@ -3899,28 +3899,28 @@
         <v>1868.4</v>
       </c>
       <c r="M32">
-        <v>374.163381</v>
+        <v>386.6354937</v>
       </c>
       <c r="N32">
-        <v>1494.236619</v>
+        <v>1481.7645063</v>
       </c>
       <c r="O32">
-        <v>373.55915475</v>
+        <v>370.441126575</v>
       </c>
       <c r="P32">
-        <v>1120.67746425</v>
+        <v>1111.323379725</v>
       </c>
       <c r="Q32">
-        <v>1663.97746425</v>
+        <v>1654.623379725</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1054913361369536</v>
+        <v>0.1061927619434983</v>
       </c>
       <c r="T32">
-        <v>1.196432845115793</v>
+        <v>1.210491985481431</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.993540508978883</v>
+        <v>4.832458557076339</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08589775574101385</v>
+        <v>0.08573407618616016</v>
       </c>
       <c r="C33">
-        <v>17107.31153841009</v>
+        <v>16951.26246055504</v>
       </c>
       <c r="D33">
-        <v>24020.57053841009</v>
+        <v>24094.21046055504</v>
       </c>
       <c r="E33">
-        <v>3791.659000000001</v>
+        <v>4021.348000000001</v>
       </c>
       <c r="F33">
-        <v>7120.359</v>
+        <v>7350.048000000001</v>
       </c>
       <c r="G33">
         <v>207.1</v>
@@ -3981,28 +3981,28 @@
         <v>1868.4</v>
       </c>
       <c r="M33">
-        <v>386.6354937</v>
+        <v>399.1076064000001</v>
       </c>
       <c r="N33">
-        <v>1481.7645063</v>
+        <v>1469.2923936</v>
       </c>
       <c r="O33">
-        <v>370.441126575</v>
+        <v>367.3230984</v>
       </c>
       <c r="P33">
-        <v>1111.323379725</v>
+        <v>1101.9692952</v>
       </c>
       <c r="Q33">
-        <v>1654.623379725</v>
+        <v>1645.2692952</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1061927619434983</v>
+        <v>0.1069148179208238</v>
       </c>
       <c r="T33">
-        <v>1.210491985481431</v>
+        <v>1.22496462997547</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.832458557076339</v>
+        <v>4.681444227167702</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08573407618616016</v>
+        <v>0.08557039663130646</v>
       </c>
       <c r="C34">
-        <v>16951.26246055504</v>
+        <v>16795.66628735158</v>
       </c>
       <c r="D34">
-        <v>24094.21046055504</v>
+        <v>24168.30328735158</v>
       </c>
       <c r="E34">
-        <v>4021.348000000001</v>
+        <v>4251.037000000001</v>
       </c>
       <c r="F34">
-        <v>7350.048000000001</v>
+        <v>7579.737000000001</v>
       </c>
       <c r="G34">
         <v>207.1</v>
@@ -4063,28 +4063,28 @@
         <v>1868.4</v>
       </c>
       <c r="M34">
-        <v>399.1076064000001</v>
+        <v>411.5797191</v>
       </c>
       <c r="N34">
-        <v>1469.2923936</v>
+        <v>1456.8202809</v>
       </c>
       <c r="O34">
-        <v>367.3230984</v>
+        <v>364.205070225</v>
       </c>
       <c r="P34">
-        <v>1101.9692952</v>
+        <v>1092.615210675</v>
       </c>
       <c r="Q34">
-        <v>1645.2692952</v>
+        <v>1635.915210675</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1069148179208238</v>
+        <v>0.1076584278079201</v>
       </c>
       <c r="T34">
-        <v>1.22496462997547</v>
+        <v>1.239869293708137</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.681444227167702</v>
+        <v>4.539582280889894</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08557039663130646</v>
+        <v>0.08540671707645275</v>
       </c>
       <c r="C35">
-        <v>16795.66628735158</v>
+        <v>16640.52720990979</v>
       </c>
       <c r="D35">
-        <v>24168.30328735158</v>
+        <v>24242.85320990979</v>
       </c>
       <c r="E35">
-        <v>4251.037000000001</v>
+        <v>4480.726000000001</v>
       </c>
       <c r="F35">
-        <v>7579.737000000001</v>
+        <v>7809.426000000001</v>
       </c>
       <c r="G35">
         <v>207.1</v>
@@ -4145,28 +4145,28 @@
         <v>1868.4</v>
       </c>
       <c r="M35">
-        <v>411.5797191</v>
+        <v>424.0518318000001</v>
       </c>
       <c r="N35">
-        <v>1456.8202809</v>
+        <v>1444.3481682</v>
       </c>
       <c r="O35">
-        <v>364.205070225</v>
+        <v>361.08704205</v>
       </c>
       <c r="P35">
-        <v>1092.615210675</v>
+        <v>1083.26112615</v>
       </c>
       <c r="Q35">
-        <v>1635.915210675</v>
+        <v>1626.56112615</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1076584278079201</v>
+        <v>0.1084245713279587</v>
       </c>
       <c r="T35">
-        <v>1.239869293708137</v>
+        <v>1.255225613917552</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.539582280889894</v>
+        <v>4.406065154981368</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08540671707645275</v>
+        <v>0.08524303752159906</v>
       </c>
       <c r="C36">
-        <v>16640.52720990979</v>
+        <v>16485.84947121163</v>
       </c>
       <c r="D36">
-        <v>24242.85320990979</v>
+        <v>24317.86447121163</v>
       </c>
       <c r="E36">
-        <v>4480.726000000001</v>
+        <v>4710.415000000002</v>
       </c>
       <c r="F36">
-        <v>7809.426000000001</v>
+        <v>8039.115000000002</v>
       </c>
       <c r="G36">
         <v>207.1</v>
@@ -4227,28 +4227,28 @@
         <v>1868.4</v>
       </c>
       <c r="M36">
-        <v>424.0518318000001</v>
+        <v>436.5239445000001</v>
       </c>
       <c r="N36">
-        <v>1444.3481682</v>
+        <v>1431.8760555</v>
       </c>
       <c r="O36">
-        <v>361.08704205</v>
+        <v>357.969013875</v>
       </c>
       <c r="P36">
-        <v>1083.26112615</v>
+        <v>1073.907041625</v>
       </c>
       <c r="Q36">
-        <v>1626.56112615</v>
+        <v>1617.207041625</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1084245713279587</v>
+        <v>0.1092142884947678</v>
       </c>
       <c r="T36">
-        <v>1.255225613917552</v>
+        <v>1.271054436287256</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.406065154981368</v>
+        <v>4.280177579124757</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08524303752159906</v>
+        <v>0.08534935796674538</v>
       </c>
       <c r="C37">
-        <v>16485.84947121163</v>
+        <v>16207.3830846794</v>
       </c>
       <c r="D37">
-        <v>24317.86447121163</v>
+        <v>24269.0870846794</v>
       </c>
       <c r="E37">
-        <v>4710.415000000002</v>
+        <v>4940.104000000002</v>
       </c>
       <c r="F37">
-        <v>8039.115000000002</v>
+        <v>8268.804000000002</v>
       </c>
       <c r="G37">
         <v>207.1</v>
@@ -4309,45 +4309,45 @@
         <v>1868.4</v>
       </c>
       <c r="M37">
-        <v>436.5239445000001</v>
+        <v>457.2648612000001</v>
       </c>
       <c r="N37">
-        <v>1431.8760555</v>
+        <v>1411.1351388</v>
       </c>
       <c r="O37">
-        <v>357.969013875</v>
+        <v>352.7837847</v>
       </c>
       <c r="P37">
-        <v>1073.907041625</v>
+        <v>1058.3513541</v>
       </c>
       <c r="Q37">
-        <v>1617.207041625</v>
+        <v>1601.6513541</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1092142884947678</v>
+        <v>0.1100286843230397</v>
       </c>
       <c r="T37">
-        <v>1.271054436287256</v>
+        <v>1.287377909356014</v>
       </c>
       <c r="U37">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.280177579124757</v>
+        <v>4.08603450327838</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08534935796674539</v>
+        <v>0.0851931784118917</v>
       </c>
       <c r="C38">
-        <v>16207.3830846794</v>
+        <v>16049.41328658995</v>
       </c>
       <c r="D38">
-        <v>24269.0870846794</v>
+        <v>24340.80628658995</v>
       </c>
       <c r="E38">
-        <v>4940.104</v>
+        <v>5169.793000000001</v>
       </c>
       <c r="F38">
-        <v>8268.804</v>
+        <v>8498.493</v>
       </c>
       <c r="G38">
         <v>207.1</v>
@@ -4391,28 +4391,28 @@
         <v>1868.4</v>
       </c>
       <c r="M38">
-        <v>457.2648612</v>
+        <v>469.9666629</v>
       </c>
       <c r="N38">
-        <v>1411.1351388</v>
+        <v>1398.4333371</v>
       </c>
       <c r="O38">
-        <v>352.7837847</v>
+        <v>349.608334275</v>
       </c>
       <c r="P38">
-        <v>1058.3513541</v>
+        <v>1048.825002825</v>
       </c>
       <c r="Q38">
-        <v>1601.6513541</v>
+        <v>1592.125002825</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1100286843230397</v>
+        <v>0.1108689339871297</v>
       </c>
       <c r="T38">
-        <v>1.287377909356014</v>
+        <v>1.304219587919018</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.086034503278381</v>
+        <v>3.975601138324912</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0851931784118917</v>
+        <v>0.08503699885703798</v>
       </c>
       <c r="C39">
-        <v>16049.41328658995</v>
+        <v>15891.86862928007</v>
       </c>
       <c r="D39">
-        <v>24340.80628658995</v>
+        <v>24412.95062928008</v>
       </c>
       <c r="E39">
-        <v>5169.793000000001</v>
+        <v>5399.482000000001</v>
       </c>
       <c r="F39">
-        <v>8498.493</v>
+        <v>8728.182000000001</v>
       </c>
       <c r="G39">
         <v>207.1</v>
@@ -4473,28 +4473,28 @@
         <v>1868.4</v>
       </c>
       <c r="M39">
-        <v>469.9666629</v>
+        <v>482.6684646</v>
       </c>
       <c r="N39">
-        <v>1398.4333371</v>
+        <v>1385.7315354</v>
       </c>
       <c r="O39">
-        <v>349.608334275</v>
+        <v>346.43288385</v>
       </c>
       <c r="P39">
-        <v>1048.825002825</v>
+        <v>1039.29865155</v>
       </c>
       <c r="Q39">
-        <v>1592.125002825</v>
+        <v>1582.59865155</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1108689339871297</v>
+        <v>0.1117362884790935</v>
       </c>
       <c r="T39">
-        <v>1.304219587919018</v>
+        <v>1.321604546435667</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.975601138324912</v>
+        <v>3.870980055737414</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08503699885703798</v>
+        <v>0.08488081930218429</v>
       </c>
       <c r="C40">
-        <v>15891.86862928007</v>
+        <v>15734.75290424461</v>
       </c>
       <c r="D40">
-        <v>24412.95062928008</v>
+        <v>24485.52390424461</v>
       </c>
       <c r="E40">
-        <v>5399.482000000001</v>
+        <v>5629.171000000001</v>
       </c>
       <c r="F40">
-        <v>8728.182000000001</v>
+        <v>8957.871000000001</v>
       </c>
       <c r="G40">
         <v>207.1</v>
@@ -4555,28 +4555,28 @@
         <v>1868.4</v>
       </c>
       <c r="M40">
-        <v>482.6684646</v>
+        <v>495.3702663000001</v>
       </c>
       <c r="N40">
-        <v>1385.7315354</v>
+        <v>1373.0297337</v>
       </c>
       <c r="O40">
-        <v>346.43288385</v>
+        <v>343.257433425</v>
       </c>
       <c r="P40">
-        <v>1039.29865155</v>
+        <v>1029.772300275</v>
       </c>
       <c r="Q40">
-        <v>1582.59865155</v>
+        <v>1573.072300275</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1117362884790935</v>
+        <v>0.1126320808232529</v>
       </c>
       <c r="T40">
-        <v>1.321604546435667</v>
+        <v>1.339559503592206</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.870980055737414</v>
+        <v>3.771724156872351</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08488081930218429</v>
+        <v>0.0847246397473306</v>
       </c>
       <c r="C41">
-        <v>15734.75290424461</v>
+        <v>15578.06994819725</v>
       </c>
       <c r="D41">
-        <v>24485.52390424461</v>
+        <v>24558.52994819725</v>
       </c>
       <c r="E41">
-        <v>5629.171000000001</v>
+        <v>5858.860000000001</v>
       </c>
       <c r="F41">
-        <v>8957.871000000001</v>
+        <v>9187.560000000001</v>
       </c>
       <c r="G41">
         <v>207.1</v>
@@ -4637,28 +4637,28 @@
         <v>1868.4</v>
       </c>
       <c r="M41">
-        <v>495.3702663000001</v>
+        <v>508.0720680000001</v>
       </c>
       <c r="N41">
-        <v>1373.0297337</v>
+        <v>1360.327932</v>
       </c>
       <c r="O41">
-        <v>343.257433425</v>
+        <v>340.081983</v>
       </c>
       <c r="P41">
-        <v>1029.772300275</v>
+        <v>1020.245949</v>
       </c>
       <c r="Q41">
-        <v>1573.072300275</v>
+        <v>1563.545949</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1126320808232529</v>
+        <v>0.1135577329122177</v>
       </c>
       <c r="T41">
-        <v>1.339559503592206</v>
+        <v>1.35811295932063</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.771724156872351</v>
+        <v>3.677431052950543</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0847246397473306</v>
+        <v>0.08456846019247689</v>
       </c>
       <c r="C42">
-        <v>15578.06994819725</v>
+        <v>15421.82364374677</v>
       </c>
       <c r="D42">
-        <v>24558.52994819725</v>
+        <v>24631.97264374678</v>
       </c>
       <c r="E42">
-        <v>5858.860000000001</v>
+        <v>6088.549000000002</v>
       </c>
       <c r="F42">
-        <v>9187.560000000001</v>
+        <v>9417.249000000002</v>
       </c>
       <c r="G42">
         <v>207.1</v>
@@ -4719,28 +4719,28 @@
         <v>1868.4</v>
       </c>
       <c r="M42">
-        <v>508.0720680000001</v>
+        <v>520.7738697000001</v>
       </c>
       <c r="N42">
-        <v>1360.327932</v>
+        <v>1347.6261303</v>
       </c>
       <c r="O42">
-        <v>340.081983</v>
+        <v>336.906532575</v>
       </c>
       <c r="P42">
-        <v>1020.245949</v>
+        <v>1010.719597725</v>
       </c>
       <c r="Q42">
-        <v>1563.545949</v>
+        <v>1554.019597725</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1135577329122177</v>
+        <v>0.1145147630380964</v>
       </c>
       <c r="T42">
-        <v>1.35811295932063</v>
+        <v>1.377295345751712</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.677431052950543</v>
+        <v>3.587737612634676</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08456846019247689</v>
+        <v>0.08441228063762321</v>
       </c>
       <c r="C43">
-        <v>15421.82364374677</v>
+        <v>15266.01792008523</v>
       </c>
       <c r="D43">
-        <v>24631.97264374678</v>
+        <v>24705.85592008523</v>
       </c>
       <c r="E43">
-        <v>6088.549000000002</v>
+        <v>6318.238000000002</v>
       </c>
       <c r="F43">
-        <v>9417.249000000002</v>
+        <v>9646.938000000002</v>
       </c>
       <c r="G43">
         <v>207.1</v>
@@ -4801,28 +4801,28 @@
         <v>1868.4</v>
       </c>
       <c r="M43">
-        <v>520.7738697000001</v>
+        <v>533.4756714000001</v>
       </c>
       <c r="N43">
-        <v>1347.6261303</v>
+        <v>1334.9243286</v>
       </c>
       <c r="O43">
-        <v>336.906532575</v>
+        <v>333.73108215</v>
       </c>
       <c r="P43">
-        <v>1010.719597725</v>
+        <v>1001.19324645</v>
       </c>
       <c r="Q43">
-        <v>1554.019597725</v>
+        <v>1544.49324645</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1145147630380964</v>
+        <v>0.1155047942027986</v>
       </c>
       <c r="T43">
-        <v>1.377295345751712</v>
+        <v>1.397139193783866</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.587737612634676</v>
+        <v>3.502315288524326</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08441228063762321</v>
+        <v>0.0842561010827695</v>
       </c>
       <c r="C44">
-        <v>15266.01792008523</v>
+        <v>15110.65675368879</v>
       </c>
       <c r="D44">
-        <v>24705.85592008523</v>
+        <v>24780.18375368879</v>
       </c>
       <c r="E44">
-        <v>6318.238</v>
+        <v>6547.927000000001</v>
       </c>
       <c r="F44">
-        <v>9646.938</v>
+        <v>9876.627</v>
       </c>
       <c r="G44">
         <v>207.1</v>
@@ -4883,28 +4883,28 @@
         <v>1868.4</v>
       </c>
       <c r="M44">
-        <v>533.4756714</v>
+        <v>546.1774731</v>
       </c>
       <c r="N44">
-        <v>1334.9243286</v>
+        <v>1322.2225269</v>
       </c>
       <c r="O44">
-        <v>333.73108215</v>
+        <v>330.555631725</v>
       </c>
       <c r="P44">
-        <v>1001.19324645</v>
+        <v>991.666895175</v>
       </c>
       <c r="Q44">
-        <v>1544.49324645</v>
+        <v>1534.966895175</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1155047942027986</v>
+        <v>0.1165295633031044</v>
       </c>
       <c r="T44">
-        <v>1.397139193783866</v>
+        <v>1.41767931718557</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.502315288524327</v>
+        <v>3.420866095767947</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0842561010827695</v>
+        <v>0.08409992152791582</v>
       </c>
       <c r="C45">
-        <v>15110.65675368879</v>
+        <v>14955.74416903106</v>
       </c>
       <c r="D45">
-        <v>24780.18375368879</v>
+        <v>24854.96016903106</v>
       </c>
       <c r="E45">
-        <v>6547.927000000001</v>
+        <v>6777.616000000001</v>
       </c>
       <c r="F45">
-        <v>9876.627</v>
+        <v>10106.316</v>
       </c>
       <c r="G45">
         <v>207.1</v>
@@ -4965,28 +4965,28 @@
         <v>1868.4</v>
       </c>
       <c r="M45">
-        <v>546.1774731</v>
+        <v>558.8792748000001</v>
       </c>
       <c r="N45">
-        <v>1322.2225269</v>
+        <v>1309.5207252</v>
       </c>
       <c r="O45">
-        <v>330.555631725</v>
+        <v>327.3801813</v>
       </c>
       <c r="P45">
-        <v>991.666895175</v>
+        <v>982.1405439</v>
       </c>
       <c r="Q45">
-        <v>1534.966895175</v>
+        <v>1525.4405439</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1165295633031044</v>
+        <v>0.1175909312998497</v>
       </c>
       <c r="T45">
-        <v>1.41767931718557</v>
+        <v>1.438953016423048</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.420866095767947</v>
+        <v>3.343119139045948</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08409992152791582</v>
+        <v>0.08394374197306212</v>
       </c>
       <c r="C46">
-        <v>14955.74416903106</v>
+        <v>14801.28423930955</v>
       </c>
       <c r="D46">
-        <v>24854.96016903106</v>
+        <v>24930.18923930955</v>
       </c>
       <c r="E46">
-        <v>6777.616000000001</v>
+        <v>7007.305000000001</v>
       </c>
       <c r="F46">
-        <v>10106.316</v>
+        <v>10336.005</v>
       </c>
       <c r="G46">
         <v>207.1</v>
@@ -5047,28 +5047,28 @@
         <v>1868.4</v>
       </c>
       <c r="M46">
-        <v>558.8792748000001</v>
+        <v>571.5810765000001</v>
       </c>
       <c r="N46">
-        <v>1309.5207252</v>
+        <v>1296.8189235</v>
       </c>
       <c r="O46">
-        <v>327.3801813</v>
+        <v>324.204730875</v>
       </c>
       <c r="P46">
-        <v>982.1405439</v>
+        <v>972.614192625</v>
       </c>
       <c r="Q46">
-        <v>1525.4405439</v>
+        <v>1515.914192625</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1175909312998497</v>
+        <v>0.1186908944964766</v>
       </c>
       <c r="T46">
-        <v>1.438953016423048</v>
+        <v>1.461000304723708</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.343119139045948</v>
+        <v>3.268827602622705</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08394374197306212</v>
+        <v>0.08378756241820842</v>
       </c>
       <c r="C47">
-        <v>14801.28423930955</v>
+        <v>14647.28108718521</v>
       </c>
       <c r="D47">
-        <v>24930.18923930955</v>
+        <v>25005.87508718521</v>
       </c>
       <c r="E47">
-        <v>7007.305000000001</v>
+        <v>7236.994000000002</v>
       </c>
       <c r="F47">
-        <v>10336.005</v>
+        <v>10565.694</v>
       </c>
       <c r="G47">
         <v>207.1</v>
@@ -5129,28 +5129,28 @@
         <v>1868.4</v>
       </c>
       <c r="M47">
-        <v>571.5810765000001</v>
+        <v>584.2828782000001</v>
       </c>
       <c r="N47">
-        <v>1296.8189235</v>
+        <v>1284.1171218</v>
       </c>
       <c r="O47">
-        <v>324.204730875</v>
+        <v>321.02928045</v>
       </c>
       <c r="P47">
-        <v>972.614192625</v>
+        <v>963.08784135</v>
       </c>
       <c r="Q47">
-        <v>1515.914192625</v>
+        <v>1506.38784135</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1186908944964766</v>
+        <v>0.1198315970707563</v>
       </c>
       <c r="T47">
-        <v>1.461000304723708</v>
+        <v>1.483864159257725</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.268827602622705</v>
+        <v>3.197766133000472</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08378756241820842</v>
+        <v>0.08363138286335471</v>
       </c>
       <c r="C48">
-        <v>14647.28108718521</v>
+        <v>14493.7388855356</v>
       </c>
       <c r="D48">
-        <v>25005.87508718521</v>
+        <v>25082.02188553561</v>
       </c>
       <c r="E48">
-        <v>7236.994000000002</v>
+        <v>7466.683000000002</v>
       </c>
       <c r="F48">
-        <v>10565.694</v>
+        <v>10795.383</v>
       </c>
       <c r="G48">
         <v>207.1</v>
@@ -5211,28 +5211,28 @@
         <v>1868.4</v>
       </c>
       <c r="M48">
-        <v>584.2828782000001</v>
+        <v>596.9846799000001</v>
       </c>
       <c r="N48">
-        <v>1284.1171218</v>
+        <v>1271.4153201</v>
       </c>
       <c r="O48">
-        <v>321.02928045</v>
+        <v>317.853830025</v>
       </c>
       <c r="P48">
-        <v>963.08784135</v>
+        <v>953.5614900749999</v>
       </c>
       <c r="Q48">
-        <v>1506.38784135</v>
+        <v>1496.861490075</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1198315970707563</v>
+        <v>0.1210153450251976</v>
       </c>
       <c r="T48">
-        <v>1.483864159257725</v>
+        <v>1.50759080075529</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.197766133000472</v>
+        <v>3.12972855570259</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08363138286335471</v>
+        <v>0.08347520330850103</v>
       </c>
       <c r="C49">
-        <v>14493.7388855356</v>
+        <v>14340.66185822177</v>
       </c>
       <c r="D49">
-        <v>25082.02188553561</v>
+        <v>25158.63385822178</v>
       </c>
       <c r="E49">
-        <v>7466.683000000002</v>
+        <v>7696.372000000002</v>
       </c>
       <c r="F49">
-        <v>10795.383</v>
+        <v>11025.072</v>
       </c>
       <c r="G49">
         <v>207.1</v>
@@ -5293,28 +5293,28 @@
         <v>1868.4</v>
       </c>
       <c r="M49">
-        <v>596.9846799000001</v>
+        <v>609.6864816000001</v>
       </c>
       <c r="N49">
-        <v>1271.4153201</v>
+        <v>1258.7135184</v>
       </c>
       <c r="O49">
-        <v>317.853830025</v>
+        <v>314.6783796</v>
       </c>
       <c r="P49">
-        <v>953.5614900749999</v>
+        <v>944.0351387999999</v>
       </c>
       <c r="Q49">
-        <v>1496.861490075</v>
+        <v>1487.3351388</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1210153450251976</v>
+        <v>0.1222446217471174</v>
       </c>
       <c r="T49">
-        <v>1.50759080075529</v>
+        <v>1.532230005387377</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.12972855570259</v>
+        <v>3.064525877458785</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08347520330850103</v>
+        <v>0.08331902375364733</v>
       </c>
       <c r="C50">
-        <v>14340.66185822177</v>
+        <v>14188.05428086932</v>
       </c>
       <c r="D50">
-        <v>25158.63385822178</v>
+        <v>25235.71528086932</v>
       </c>
       <c r="E50">
-        <v>7696.372</v>
+        <v>7926.061000000001</v>
       </c>
       <c r="F50">
-        <v>11025.072</v>
+        <v>11254.761</v>
       </c>
       <c r="G50">
         <v>207.1</v>
@@ -5375,28 +5375,28 @@
         <v>1868.4</v>
       </c>
       <c r="M50">
-        <v>609.6864816</v>
+        <v>622.3882833</v>
       </c>
       <c r="N50">
-        <v>1258.7135184</v>
+        <v>1246.0117167</v>
       </c>
       <c r="O50">
-        <v>314.6783796</v>
+        <v>311.502929175</v>
       </c>
       <c r="P50">
-        <v>944.0351388000001</v>
+        <v>934.5087875250001</v>
       </c>
       <c r="Q50">
-        <v>1487.3351388</v>
+        <v>1477.808787525</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1222446217471174</v>
+        <v>0.1235221053993085</v>
       </c>
       <c r="T50">
-        <v>1.532230005387377</v>
+        <v>1.55783545333837</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.064525877458786</v>
+        <v>3.001984533020852</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08331902375364733</v>
+        <v>0.08410034419879363</v>
       </c>
       <c r="C51">
-        <v>14188.05428086932</v>
+        <v>13577.40719158234</v>
       </c>
       <c r="D51">
-        <v>25235.71528086932</v>
+        <v>24854.75719158234</v>
       </c>
       <c r="E51">
-        <v>7926.061000000001</v>
+        <v>8155.750000000001</v>
       </c>
       <c r="F51">
-        <v>11254.761</v>
+        <v>11484.45</v>
       </c>
       <c r="G51">
         <v>207.1</v>
@@ -5457,45 +5457,45 @@
         <v>1868.4</v>
       </c>
       <c r="M51">
-        <v>622.3882833</v>
+        <v>663.8012100000001</v>
       </c>
       <c r="N51">
-        <v>1246.0117167</v>
+        <v>1204.59879</v>
       </c>
       <c r="O51">
-        <v>311.502929175</v>
+        <v>301.1496975</v>
       </c>
       <c r="P51">
-        <v>934.5087875250001</v>
+        <v>903.4490925</v>
       </c>
       <c r="Q51">
-        <v>1477.808787525</v>
+        <v>1446.7490925</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1235221053993085</v>
+        <v>0.1248506883975873</v>
       </c>
       <c r="T51">
-        <v>1.55783545333837</v>
+        <v>1.584465119207402</v>
       </c>
       <c r="U51">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.001984533020852</v>
+        <v>2.814698093123392</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08410034419879363</v>
+        <v>0.08396291464393994</v>
       </c>
       <c r="C52">
-        <v>13577.40719158234</v>
+        <v>13413.8905738281</v>
       </c>
       <c r="D52">
-        <v>24854.75719158234</v>
+        <v>24920.9295738281</v>
       </c>
       <c r="E52">
-        <v>8155.750000000001</v>
+        <v>8385.439000000002</v>
       </c>
       <c r="F52">
-        <v>11484.45</v>
+        <v>11714.139</v>
       </c>
       <c r="G52">
         <v>207.1</v>
@@ -5539,28 +5539,28 @@
         <v>1868.4</v>
       </c>
       <c r="M52">
-        <v>663.8012100000001</v>
+        <v>677.0772342000001</v>
       </c>
       <c r="N52">
-        <v>1204.59879</v>
+        <v>1191.3227658</v>
       </c>
       <c r="O52">
-        <v>301.1496975</v>
+        <v>297.83069145</v>
       </c>
       <c r="P52">
-        <v>903.4490925</v>
+        <v>893.4920743500001</v>
       </c>
       <c r="Q52">
-        <v>1446.7490925</v>
+        <v>1436.79207435</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1248506883975873</v>
+        <v>0.1262334992733468</v>
       </c>
       <c r="T52">
-        <v>1.584465119207402</v>
+        <v>1.612181710213945</v>
       </c>
       <c r="U52">
         <v>0.0578</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.814698093123392</v>
+        <v>2.759507934434697</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08396291464393994</v>
+        <v>0.08382548508908623</v>
       </c>
       <c r="C53">
-        <v>13413.8905738281</v>
+        <v>13250.72724644568</v>
       </c>
       <c r="D53">
-        <v>24920.9295738281</v>
+        <v>24987.45524644569</v>
       </c>
       <c r="E53">
-        <v>8385.439000000002</v>
+        <v>8615.128000000001</v>
       </c>
       <c r="F53">
-        <v>11714.139</v>
+        <v>11943.828</v>
       </c>
       <c r="G53">
         <v>207.1</v>
@@ -5621,28 +5621,28 @@
         <v>1868.4</v>
       </c>
       <c r="M53">
-        <v>677.0772342000001</v>
+        <v>690.3532584000001</v>
       </c>
       <c r="N53">
-        <v>1191.3227658</v>
+        <v>1178.0467416</v>
       </c>
       <c r="O53">
-        <v>297.83069145</v>
+        <v>294.5116854</v>
       </c>
       <c r="P53">
-        <v>893.4920743500001</v>
+        <v>883.5350562000001</v>
       </c>
       <c r="Q53">
-        <v>1436.79207435</v>
+        <v>1426.8350562</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1262334992733468</v>
+        <v>0.1276739272689296</v>
       </c>
       <c r="T53">
-        <v>1.612181710213945</v>
+        <v>1.641053159179094</v>
       </c>
       <c r="U53">
         <v>0.0578</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.759507934434697</v>
+        <v>2.706440474157107</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08382548508908623</v>
+        <v>0.08368805553423254</v>
       </c>
       <c r="C54">
-        <v>13250.72724644568</v>
+        <v>13087.92004630211</v>
       </c>
       <c r="D54">
-        <v>24987.45524644569</v>
+        <v>25054.33704630211</v>
       </c>
       <c r="E54">
-        <v>8615.128000000001</v>
+        <v>8844.817000000003</v>
       </c>
       <c r="F54">
-        <v>11943.828</v>
+        <v>12173.517</v>
       </c>
       <c r="G54">
         <v>207.1</v>
@@ -5703,28 +5703,28 @@
         <v>1868.4</v>
       </c>
       <c r="M54">
-        <v>690.3532584000001</v>
+        <v>703.6292826000001</v>
       </c>
       <c r="N54">
-        <v>1178.0467416</v>
+        <v>1164.7707174</v>
       </c>
       <c r="O54">
-        <v>294.5116854</v>
+        <v>291.19267935</v>
       </c>
       <c r="P54">
-        <v>883.5350562000001</v>
+        <v>873.57803805</v>
       </c>
       <c r="Q54">
-        <v>1426.8350562</v>
+        <v>1416.87803805</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1276739272689296</v>
+        <v>0.1291756500728352</v>
       </c>
       <c r="T54">
-        <v>1.641053159179094</v>
+        <v>1.671153180440633</v>
       </c>
       <c r="U54">
         <v>0.0578</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.706440474157107</v>
+        <v>2.655375559550369</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08368805553423254</v>
+        <v>0.08355062597937885</v>
       </c>
       <c r="C55">
-        <v>13087.92004630211</v>
+        <v>12925.47184071872</v>
       </c>
       <c r="D55">
-        <v>25054.33704630211</v>
+        <v>25121.57784071872</v>
       </c>
       <c r="E55">
-        <v>8844.817000000003</v>
+        <v>9074.506000000001</v>
       </c>
       <c r="F55">
-        <v>12173.517</v>
+        <v>12403.206</v>
       </c>
       <c r="G55">
         <v>207.1</v>
@@ -5785,28 +5785,28 @@
         <v>1868.4</v>
       </c>
       <c r="M55">
-        <v>703.6292826000001</v>
+        <v>716.9053068000002</v>
       </c>
       <c r="N55">
-        <v>1164.7707174</v>
+        <v>1151.4946932</v>
       </c>
       <c r="O55">
-        <v>291.19267935</v>
+        <v>287.8736733</v>
       </c>
       <c r="P55">
-        <v>873.57803805</v>
+        <v>863.6210198999999</v>
       </c>
       <c r="Q55">
-        <v>1416.87803805</v>
+        <v>1406.921019899999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1291756500728352</v>
+        <v>0.1307426651725627</v>
       </c>
       <c r="T55">
-        <v>1.671153180440633</v>
+        <v>1.702561898278761</v>
       </c>
       <c r="U55">
         <v>0.0578</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.655375559550369</v>
+        <v>2.606201938077214</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08355062597937885</v>
+        <v>0.08341319642452516</v>
       </c>
       <c r="C56">
-        <v>12925.47184071872</v>
+        <v>12763.38552788094</v>
       </c>
       <c r="D56">
-        <v>25121.57784071872</v>
+        <v>25189.18052788094</v>
       </c>
       <c r="E56">
-        <v>9074.506000000001</v>
+        <v>9304.195000000003</v>
       </c>
       <c r="F56">
-        <v>12403.206</v>
+        <v>12632.895</v>
       </c>
       <c r="G56">
         <v>207.1</v>
@@ -5867,28 +5867,28 @@
         <v>1868.4</v>
       </c>
       <c r="M56">
-        <v>716.9053068000002</v>
+        <v>730.1813310000002</v>
       </c>
       <c r="N56">
-        <v>1151.4946932</v>
+        <v>1138.218669</v>
       </c>
       <c r="O56">
-        <v>287.8736733</v>
+        <v>284.55466725</v>
       </c>
       <c r="P56">
-        <v>863.6210198999999</v>
+        <v>853.6640017499999</v>
       </c>
       <c r="Q56">
-        <v>1406.921019899999</v>
+        <v>1396.96400175</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1307426651725627</v>
+        <v>0.1323793253878337</v>
       </c>
       <c r="T56">
-        <v>1.702561898278761</v>
+        <v>1.735366559131916</v>
       </c>
       <c r="U56">
         <v>0.0578</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.606201938077214</v>
+        <v>2.558816448293991</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08341319642452516</v>
+        <v>0.08327576686967145</v>
       </c>
       <c r="C57">
-        <v>12763.38552788094</v>
+        <v>12601.6640372547</v>
       </c>
       <c r="D57">
-        <v>25189.18052788094</v>
+        <v>25257.1480372547</v>
       </c>
       <c r="E57">
-        <v>9304.195000000003</v>
+        <v>9533.884000000002</v>
       </c>
       <c r="F57">
-        <v>12632.895</v>
+        <v>12862.584</v>
       </c>
       <c r="G57">
         <v>207.1</v>
@@ -5949,28 +5949,28 @@
         <v>1868.4</v>
       </c>
       <c r="M57">
-        <v>730.1813310000002</v>
+        <v>743.4573552000002</v>
       </c>
       <c r="N57">
-        <v>1138.218669</v>
+        <v>1124.9426448</v>
       </c>
       <c r="O57">
-        <v>284.55466725</v>
+        <v>281.2356612</v>
       </c>
       <c r="P57">
-        <v>853.6640017499999</v>
+        <v>843.7069835999999</v>
       </c>
       <c r="Q57">
-        <v>1396.96400175</v>
+        <v>1387.0069836</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1323793253878337</v>
+        <v>0.1340903792492533</v>
       </c>
       <c r="T57">
-        <v>1.735366559131916</v>
+        <v>1.769662340932942</v>
       </c>
       <c r="U57">
         <v>0.0578</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.558816448293991</v>
+        <v>2.513123297431599</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08327576686967145</v>
+        <v>0.08463458731481777</v>
       </c>
       <c r="C58">
-        <v>12601.6640372547</v>
+        <v>11715.65012629118</v>
       </c>
       <c r="D58">
-        <v>25257.1480372547</v>
+        <v>24600.82312629118</v>
       </c>
       <c r="E58">
-        <v>9533.884000000002</v>
+        <v>9763.573000000004</v>
       </c>
       <c r="F58">
-        <v>12862.584</v>
+        <v>13092.273</v>
       </c>
       <c r="G58">
         <v>207.1</v>
@@ -6031,45 +6031,45 @@
         <v>1868.4</v>
       </c>
       <c r="M58">
-        <v>743.4573552000002</v>
+        <v>802.5563349000001</v>
       </c>
       <c r="N58">
-        <v>1124.9426448</v>
+        <v>1065.8436651</v>
       </c>
       <c r="O58">
-        <v>281.2356612</v>
+        <v>266.460916275</v>
       </c>
       <c r="P58">
-        <v>843.7069835999999</v>
+        <v>799.3827488249999</v>
       </c>
       <c r="Q58">
-        <v>1387.0069836</v>
+        <v>1342.682748825</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1340903792492533</v>
+        <v>0.1358810170112041</v>
       </c>
       <c r="T58">
-        <v>1.769662340932942</v>
+        <v>1.805553275375877</v>
       </c>
       <c r="U58">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V58">
         <v>0.25</v>
       </c>
       <c r="W58">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.513123297431599</v>
+        <v>2.328060870932887</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08463458731481777</v>
+        <v>0.08452340775996407</v>
       </c>
       <c r="C59">
-        <v>11715.65012629118</v>
+        <v>11538.37803936514</v>
       </c>
       <c r="D59">
-        <v>24600.82312629118</v>
+        <v>24653.24003936514</v>
       </c>
       <c r="E59">
-        <v>9763.573000000004</v>
+        <v>9993.262000000002</v>
       </c>
       <c r="F59">
-        <v>13092.273</v>
+        <v>13321.962</v>
       </c>
       <c r="G59">
         <v>207.1</v>
@@ -6113,28 +6113,28 @@
         <v>1868.4</v>
       </c>
       <c r="M59">
-        <v>802.5563349000001</v>
+        <v>816.6362706000002</v>
       </c>
       <c r="N59">
-        <v>1065.8436651</v>
+        <v>1051.7637294</v>
       </c>
       <c r="O59">
-        <v>266.460916275</v>
+        <v>262.94093235</v>
       </c>
       <c r="P59">
-        <v>799.3827488249999</v>
+        <v>788.82279705</v>
       </c>
       <c r="Q59">
-        <v>1342.682748825</v>
+        <v>1332.12279705</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1358810170112041</v>
+        <v>0.1377569232380097</v>
       </c>
       <c r="T59">
-        <v>1.805553275375877</v>
+        <v>1.843153301935141</v>
       </c>
       <c r="U59">
         <v>0.0613</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.328060870932887</v>
+        <v>2.287921890399561</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08452340775996406</v>
+        <v>0.08565122820511037</v>
       </c>
       <c r="C60">
-        <v>11538.37803936515</v>
+        <v>10787.10539124043</v>
       </c>
       <c r="D60">
-        <v>24653.24003936515</v>
+        <v>24131.65639124043</v>
       </c>
       <c r="E60">
-        <v>9993.261999999999</v>
+        <v>10222.951</v>
       </c>
       <c r="F60">
-        <v>13321.962</v>
+        <v>13551.651</v>
       </c>
       <c r="G60">
         <v>207.1</v>
@@ -6195,45 +6195,45 @@
         <v>1868.4</v>
       </c>
       <c r="M60">
-        <v>816.6362706</v>
+        <v>868.6608291</v>
       </c>
       <c r="N60">
-        <v>1051.7637294</v>
+        <v>999.7391709000001</v>
       </c>
       <c r="O60">
-        <v>262.94093235</v>
+        <v>249.934792725</v>
       </c>
       <c r="P60">
-        <v>788.8227970500001</v>
+        <v>749.804378175</v>
       </c>
       <c r="Q60">
-        <v>1332.12279705</v>
+        <v>1293.104378175</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1377569232380097</v>
+        <v>0.139724337085635</v>
       </c>
       <c r="T60">
-        <v>1.84315330193514</v>
+        <v>1.882587476131442</v>
       </c>
       <c r="U60">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V60">
         <v>0.25</v>
       </c>
       <c r="W60">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.287921890399562</v>
+        <v>2.15089703300632</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08565122820511037</v>
+        <v>0.08556104865025668</v>
       </c>
       <c r="C61">
-        <v>10787.10539124043</v>
+        <v>10598.30859623905</v>
       </c>
       <c r="D61">
-        <v>24131.65639124043</v>
+        <v>24172.54859623905</v>
       </c>
       <c r="E61">
-        <v>10222.951</v>
+        <v>10452.64</v>
       </c>
       <c r="F61">
-        <v>13551.651</v>
+        <v>13781.34</v>
       </c>
       <c r="G61">
         <v>207.1</v>
@@ -6277,28 +6277,28 @@
         <v>1868.4</v>
       </c>
       <c r="M61">
-        <v>868.6608291</v>
+        <v>883.3838940000001</v>
       </c>
       <c r="N61">
-        <v>999.7391709000001</v>
+        <v>985.016106</v>
       </c>
       <c r="O61">
-        <v>249.934792725</v>
+        <v>246.2540265</v>
       </c>
       <c r="P61">
-        <v>749.804378175</v>
+        <v>738.7620795</v>
       </c>
       <c r="Q61">
-        <v>1293.104378175</v>
+        <v>1282.0620795</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.139724337085635</v>
+        <v>0.1417901216256417</v>
       </c>
       <c r="T61">
-        <v>1.882587476131442</v>
+        <v>1.923993359037559</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.15089703300632</v>
+        <v>2.115048749122881</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08556104865025668</v>
+        <v>0.08547086909540298</v>
       </c>
       <c r="C62">
-        <v>10598.30859623905</v>
+        <v>10409.65062393477</v>
       </c>
       <c r="D62">
-        <v>24172.54859623905</v>
+        <v>24213.57962393477</v>
       </c>
       <c r="E62">
-        <v>10452.64</v>
+        <v>10682.329</v>
       </c>
       <c r="F62">
-        <v>13781.34</v>
+        <v>14011.029</v>
       </c>
       <c r="G62">
         <v>207.1</v>
@@ -6359,28 +6359,28 @@
         <v>1868.4</v>
       </c>
       <c r="M62">
-        <v>883.3838940000001</v>
+        <v>898.1069589000001</v>
       </c>
       <c r="N62">
-        <v>985.016106</v>
+        <v>970.2930411</v>
       </c>
       <c r="O62">
-        <v>246.2540265</v>
+        <v>242.573260275</v>
       </c>
       <c r="P62">
-        <v>738.7620795</v>
+        <v>727.719780825</v>
       </c>
       <c r="Q62">
-        <v>1282.0620795</v>
+        <v>1271.019780825</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1417901216256417</v>
+        <v>0.1439618438343666</v>
       </c>
       <c r="T62">
-        <v>1.923993359037559</v>
+        <v>1.967522620554246</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.115048749122881</v>
+        <v>2.080375818809391</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08547086909540298</v>
+        <v>0.0853806895405493</v>
       </c>
       <c r="C63">
-        <v>10409.65062393477</v>
+        <v>10221.13218245187</v>
       </c>
       <c r="D63">
-        <v>24213.57962393477</v>
+        <v>24254.75018245187</v>
       </c>
       <c r="E63">
-        <v>10682.329</v>
+        <v>10912.018</v>
       </c>
       <c r="F63">
-        <v>14011.029</v>
+        <v>14240.718</v>
       </c>
       <c r="G63">
         <v>207.1</v>
@@ -6441,28 +6441,28 @@
         <v>1868.4</v>
       </c>
       <c r="M63">
-        <v>898.1069589000001</v>
+        <v>912.8300238000002</v>
       </c>
       <c r="N63">
-        <v>970.2930411</v>
+        <v>955.5699761999999</v>
       </c>
       <c r="O63">
-        <v>242.573260275</v>
+        <v>238.89249405</v>
       </c>
       <c r="P63">
-        <v>727.719780825</v>
+        <v>716.6774821499999</v>
       </c>
       <c r="Q63">
-        <v>1271.019780825</v>
+        <v>1259.97748215</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1439618438343666</v>
+        <v>0.1462478672119718</v>
       </c>
       <c r="T63">
-        <v>1.967522620554246</v>
+        <v>2.013342895834969</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.080375818809391</v>
+        <v>2.046821370118917</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.0853806895405493</v>
+        <v>0.0852905099856956</v>
       </c>
       <c r="C64">
-        <v>10221.13218245187</v>
+        <v>10032.75398473897</v>
       </c>
       <c r="D64">
-        <v>24254.75018245187</v>
+        <v>24296.06098473897</v>
       </c>
       <c r="E64">
-        <v>10912.018</v>
+        <v>11141.707</v>
       </c>
       <c r="F64">
-        <v>14240.718</v>
+        <v>14470.407</v>
       </c>
       <c r="G64">
         <v>207.1</v>
@@ -6523,28 +6523,28 @@
         <v>1868.4</v>
       </c>
       <c r="M64">
-        <v>912.8300238000002</v>
+        <v>927.5530887000001</v>
       </c>
       <c r="N64">
-        <v>955.5699761999999</v>
+        <v>940.8469113</v>
       </c>
       <c r="O64">
-        <v>238.89249405</v>
+        <v>235.211727825</v>
       </c>
       <c r="P64">
-        <v>716.6774821499999</v>
+        <v>705.635183475</v>
       </c>
       <c r="Q64">
-        <v>1259.97748215</v>
+        <v>1248.935183475</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1462478672119718</v>
+        <v>0.1486574594207989</v>
       </c>
       <c r="T64">
-        <v>2.013342895834969</v>
+        <v>2.061639942752488</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.046821370118917</v>
+        <v>2.014332142021792</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.0852905099856956</v>
+        <v>0.08894433043084188</v>
       </c>
       <c r="C65">
-        <v>10032.75398473897</v>
+        <v>8234.651988846083</v>
       </c>
       <c r="D65">
-        <v>24296.06098473897</v>
+        <v>22727.64798884609</v>
       </c>
       <c r="E65">
-        <v>11141.707</v>
+        <v>11371.396</v>
       </c>
       <c r="F65">
-        <v>14470.407</v>
+        <v>14700.096</v>
       </c>
       <c r="G65">
         <v>207.1</v>
@@ -6605,45 +6605,45 @@
         <v>1868.4</v>
       </c>
       <c r="M65">
-        <v>927.5530887000001</v>
+        <v>1056.9369024</v>
       </c>
       <c r="N65">
-        <v>940.8469113</v>
+        <v>811.4630975999999</v>
       </c>
       <c r="O65">
-        <v>235.211727825</v>
+        <v>202.8657744</v>
       </c>
       <c r="P65">
-        <v>705.635183475</v>
+        <v>608.5973231999999</v>
       </c>
       <c r="Q65">
-        <v>1248.935183475</v>
+        <v>1151.8973232</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1486574594207989</v>
+        <v>0.1512009178634497</v>
       </c>
       <c r="T65">
-        <v>2.061639942752488</v>
+        <v>2.112620158943202</v>
       </c>
       <c r="U65">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V65">
         <v>0.25</v>
       </c>
       <c r="W65">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.014332142021792</v>
+        <v>1.767749802052895</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08894433043084188</v>
+        <v>0.0908139008759882</v>
       </c>
       <c r="C66">
-        <v>8234.651988846083</v>
+        <v>7278.254193819861</v>
       </c>
       <c r="D66">
-        <v>22727.64798884609</v>
+        <v>22000.93919381986</v>
       </c>
       <c r="E66">
-        <v>11371.396</v>
+        <v>11601.085</v>
       </c>
       <c r="F66">
-        <v>14700.096</v>
+        <v>14929.785</v>
       </c>
       <c r="G66">
         <v>207.1</v>
@@ -6687,45 +6687,45 @@
         <v>1868.4</v>
       </c>
       <c r="M66">
-        <v>1056.9369024</v>
+        <v>1131.677703</v>
       </c>
       <c r="N66">
-        <v>811.4630975999999</v>
+        <v>736.7222969999998</v>
       </c>
       <c r="O66">
-        <v>202.8657744</v>
+        <v>184.1805742499999</v>
       </c>
       <c r="P66">
-        <v>608.5973231999999</v>
+        <v>552.5417227499998</v>
       </c>
       <c r="Q66">
-        <v>1151.8973232</v>
+        <v>1095.841722749999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1512009178634497</v>
+        <v>0.1538897167885377</v>
       </c>
       <c r="T66">
-        <v>2.112620158943202</v>
+        <v>2.166513530344815</v>
       </c>
       <c r="U66">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V66">
         <v>0.25</v>
       </c>
       <c r="W66">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y66">
-        <v>1.767749802052895</v>
+        <v>1.651000099274731</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0908139008759882</v>
+        <v>0.09081147132113448</v>
       </c>
       <c r="C67">
-        <v>7278.254193819861</v>
+        <v>7049.479412442794</v>
       </c>
       <c r="D67">
-        <v>22000.93919381986</v>
+        <v>22001.8534124428</v>
       </c>
       <c r="E67">
-        <v>11601.085</v>
+        <v>11830.774</v>
       </c>
       <c r="F67">
-        <v>14929.785</v>
+        <v>15159.474</v>
       </c>
       <c r="G67">
         <v>207.1</v>
@@ -6769,28 +6769,28 @@
         <v>1868.4</v>
       </c>
       <c r="M67">
-        <v>1131.677703</v>
+        <v>1149.0881292</v>
       </c>
       <c r="N67">
-        <v>736.7222969999998</v>
+        <v>719.3118708</v>
       </c>
       <c r="O67">
-        <v>184.1805742499999</v>
+        <v>179.8279677</v>
       </c>
       <c r="P67">
-        <v>552.5417227499998</v>
+        <v>539.4839030999999</v>
       </c>
       <c r="Q67">
-        <v>1095.841722749999</v>
+        <v>1082.7839031</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1538897167885377</v>
+        <v>0.1567366803562779</v>
       </c>
       <c r="T67">
-        <v>2.166513530344815</v>
+        <v>2.223577100064169</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.651000099274731</v>
+        <v>1.625984946255417</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09081147132113448</v>
+        <v>0.0908090417662808</v>
       </c>
       <c r="C68">
-        <v>7049.479412442794</v>
+        <v>6820.704707047056</v>
       </c>
       <c r="D68">
-        <v>22001.8534124428</v>
+        <v>22002.76770704706</v>
       </c>
       <c r="E68">
-        <v>11830.774</v>
+        <v>12060.463</v>
       </c>
       <c r="F68">
-        <v>15159.474</v>
+        <v>15389.163</v>
       </c>
       <c r="G68">
         <v>207.1</v>
@@ -6851,28 +6851,28 @@
         <v>1868.4</v>
       </c>
       <c r="M68">
-        <v>1149.0881292</v>
+        <v>1166.4985554</v>
       </c>
       <c r="N68">
-        <v>719.3118708</v>
+        <v>701.9014445999999</v>
       </c>
       <c r="O68">
-        <v>179.8279677</v>
+        <v>175.47536115</v>
       </c>
       <c r="P68">
-        <v>539.4839030999999</v>
+        <v>526.4260834499999</v>
       </c>
       <c r="Q68">
-        <v>1082.7839031</v>
+        <v>1069.72608345</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1567366803562779</v>
+        <v>0.1597561871705479</v>
       </c>
       <c r="T68">
-        <v>2.223577100064169</v>
+        <v>2.284099067948332</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.625984946255417</v>
+        <v>1.601716514221754</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.0908090417662808</v>
+        <v>0.09080661221142711</v>
       </c>
       <c r="C69">
-        <v>6820.704707047056</v>
+        <v>6591.930077642133</v>
       </c>
       <c r="D69">
-        <v>22002.76770704706</v>
+        <v>22003.68207764214</v>
       </c>
       <c r="E69">
-        <v>12060.463</v>
+        <v>12290.152</v>
       </c>
       <c r="F69">
-        <v>15389.163</v>
+        <v>15618.852</v>
       </c>
       <c r="G69">
         <v>207.1</v>
@@ -6933,28 +6933,28 @@
         <v>1868.4</v>
       </c>
       <c r="M69">
-        <v>1166.4985554</v>
+        <v>1183.9089816</v>
       </c>
       <c r="N69">
-        <v>701.9014445999999</v>
+        <v>684.4910183999998</v>
       </c>
       <c r="O69">
-        <v>175.47536115</v>
+        <v>171.1227546</v>
       </c>
       <c r="P69">
-        <v>526.4260834499999</v>
+        <v>513.3682637999998</v>
       </c>
       <c r="Q69">
-        <v>1069.72608345</v>
+        <v>1056.6682638</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1597561871705479</v>
+        <v>0.1629644131607097</v>
       </c>
       <c r="T69">
-        <v>2.284099067948332</v>
+        <v>2.348403658825256</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.601716514221754</v>
+        <v>1.578161859600846</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09080661221142711</v>
+        <v>0.0908041826565734</v>
       </c>
       <c r="C70">
-        <v>6591.930077642133</v>
+        <v>6363.155524237502</v>
       </c>
       <c r="D70">
-        <v>22003.68207764214</v>
+        <v>22004.59652423751</v>
       </c>
       <c r="E70">
-        <v>12290.152</v>
+        <v>12519.841</v>
       </c>
       <c r="F70">
-        <v>15618.852</v>
+        <v>15848.541</v>
       </c>
       <c r="G70">
         <v>207.1</v>
@@ -7015,28 +7015,28 @@
         <v>1868.4</v>
       </c>
       <c r="M70">
-        <v>1183.9089816</v>
+        <v>1201.3194078</v>
       </c>
       <c r="N70">
-        <v>684.4910183999998</v>
+        <v>667.0805921999997</v>
       </c>
       <c r="O70">
-        <v>171.1227546</v>
+        <v>166.7701480499999</v>
       </c>
       <c r="P70">
-        <v>513.3682637999998</v>
+        <v>500.3104441499998</v>
       </c>
       <c r="Q70">
-        <v>1056.6682638</v>
+        <v>1043.610444149999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1629644131607097</v>
+        <v>0.1663796214728175</v>
       </c>
       <c r="T70">
-        <v>2.348403658825256</v>
+        <v>2.416856932984562</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.578161859600846</v>
+        <v>1.555289948592138</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0908041826565734</v>
+        <v>0.09080175310171971</v>
       </c>
       <c r="C71">
-        <v>6363.155524237502</v>
+        <v>6134.381046842627</v>
       </c>
       <c r="D71">
-        <v>22004.59652423751</v>
+        <v>22005.51104684263</v>
       </c>
       <c r="E71">
-        <v>12519.841</v>
+        <v>12749.53</v>
       </c>
       <c r="F71">
-        <v>15848.541</v>
+        <v>16078.23</v>
       </c>
       <c r="G71">
         <v>207.1</v>
@@ -7097,28 +7097,28 @@
         <v>1868.4</v>
       </c>
       <c r="M71">
-        <v>1201.3194078</v>
+        <v>1218.729834</v>
       </c>
       <c r="N71">
-        <v>667.0805921999997</v>
+        <v>649.6701659999997</v>
       </c>
       <c r="O71">
-        <v>166.7701480499999</v>
+        <v>162.4175414999999</v>
       </c>
       <c r="P71">
-        <v>500.3104441499998</v>
+        <v>487.2526244999997</v>
       </c>
       <c r="Q71">
-        <v>1043.610444149999</v>
+        <v>1030.552624499999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1663796214728175</v>
+        <v>0.1700225103390657</v>
       </c>
       <c r="T71">
-        <v>2.416856932984562</v>
+        <v>2.489873758754489</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.555289948592138</v>
+        <v>1.533071520755107</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09080175310171971</v>
+        <v>0.09079932354686603</v>
       </c>
       <c r="C72">
-        <v>6134.381046842627</v>
+        <v>5905.606645466991</v>
       </c>
       <c r="D72">
-        <v>22005.51104684263</v>
+        <v>22006.425645467</v>
       </c>
       <c r="E72">
-        <v>12749.53</v>
+        <v>12979.219</v>
       </c>
       <c r="F72">
-        <v>16078.23</v>
+        <v>16307.919</v>
       </c>
       <c r="G72">
         <v>207.1</v>
@@ -7179,28 +7179,28 @@
         <v>1868.4</v>
       </c>
       <c r="M72">
-        <v>1218.729834</v>
+        <v>1236.1402602</v>
       </c>
       <c r="N72">
-        <v>649.6701659999997</v>
+        <v>632.2597397999998</v>
       </c>
       <c r="O72">
-        <v>162.4175414999999</v>
+        <v>158.06493495</v>
       </c>
       <c r="P72">
-        <v>487.2526244999997</v>
+        <v>474.1948048499999</v>
       </c>
       <c r="Q72">
-        <v>1030.552624499999</v>
+        <v>1017.49480485</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1700225103390657</v>
+        <v>0.1739166329202277</v>
       </c>
       <c r="T72">
-        <v>2.489873758754489</v>
+        <v>2.567926227680962</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.533071520755107</v>
+        <v>1.511478964124754</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09079932354686603</v>
+        <v>0.09846489399201233</v>
       </c>
       <c r="C73">
-        <v>5905.606645466994</v>
+        <v>3124.67287270843</v>
       </c>
       <c r="D73">
-        <v>22006.425645467</v>
+        <v>19455.18087270843</v>
       </c>
       <c r="E73">
-        <v>12979.219</v>
+        <v>13208.908</v>
       </c>
       <c r="F73">
-        <v>16307.919</v>
+        <v>16537.608</v>
       </c>
       <c r="G73">
         <v>207.1</v>
@@ -7261,45 +7261,45 @@
         <v>1868.4</v>
       </c>
       <c r="M73">
-        <v>1236.1402602</v>
+        <v>1488.38472</v>
       </c>
       <c r="N73">
-        <v>632.2597398</v>
+        <v>380.0152800000001</v>
       </c>
       <c r="O73">
-        <v>158.06493495</v>
+        <v>95.00382000000002</v>
       </c>
       <c r="P73">
-        <v>474.19480485</v>
+        <v>285.0114600000001</v>
       </c>
       <c r="Q73">
-        <v>1017.49480485</v>
+        <v>828.3114599999998</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1739166329202276</v>
+        <v>0.1780889071143297</v>
       </c>
       <c r="T73">
-        <v>2.567926227680961</v>
+        <v>2.651553872959325</v>
       </c>
       <c r="U73">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V73">
         <v>0.25</v>
       </c>
       <c r="W73">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y73">
-        <v>1.511478964124754</v>
+        <v>1.255320600173858</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09846489399201233</v>
+        <v>0.1160340723854876</v>
       </c>
       <c r="C74">
-        <v>3124.67287270843</v>
+        <v>-1189.247138606363</v>
       </c>
       <c r="D74">
-        <v>19455.18087270843</v>
+        <v>15370.94986139364</v>
       </c>
       <c r="E74">
-        <v>13208.908</v>
+        <v>13438.597</v>
       </c>
       <c r="F74">
-        <v>16537.608</v>
+        <v>16767.297</v>
       </c>
       <c r="G74">
         <v>207.1</v>
@@ -7343,45 +7343,45 @@
         <v>1868.4</v>
       </c>
       <c r="M74">
-        <v>1488.38472</v>
+        <v>1988.601424200001</v>
       </c>
       <c r="N74">
-        <v>380.0152800000001</v>
+        <v>-120.2014242000005</v>
       </c>
       <c r="O74">
-        <v>95.00382000000002</v>
+        <v>-30.05035605000012</v>
       </c>
       <c r="P74">
-        <v>285.0114600000001</v>
+        <v>-90.15106815000036</v>
       </c>
       <c r="Q74">
-        <v>828.3114599999998</v>
+        <v>453.1489318499994</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1780889071143297</v>
+        <v>0.1844158004011262</v>
       </c>
       <c r="T74">
-        <v>2.651553872959325</v>
+        <v>2.77836797071211</v>
       </c>
       <c r="U74">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V74">
-        <v>0.25</v>
+        <v>0.23488869831616</v>
       </c>
       <c r="W74">
-        <v>0.0675</v>
+        <v>0.09074220037970343</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y74">
-        <v>1.255320600173858</v>
+        <v>0.93955479326464</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1160340723854876</v>
+        <v>0.1167620723854876</v>
       </c>
       <c r="C75">
-        <v>-1189.247138606363</v>
+        <v>-1551.490552024621</v>
       </c>
       <c r="D75">
-        <v>15370.94986139364</v>
+        <v>15238.39544797538</v>
       </c>
       <c r="E75">
-        <v>13438.597</v>
+        <v>13668.286</v>
       </c>
       <c r="F75">
-        <v>16767.297</v>
+        <v>16996.986</v>
       </c>
       <c r="G75">
         <v>207.1</v>
@@ -7425,37 +7425,37 @@
         <v>1868.4</v>
       </c>
       <c r="M75">
-        <v>1988.601424200001</v>
+        <v>2015.8425396</v>
       </c>
       <c r="N75">
-        <v>-120.2014242000005</v>
+        <v>-147.4425396000001</v>
       </c>
       <c r="O75">
-        <v>-30.05035605000012</v>
+        <v>-36.86063490000004</v>
       </c>
       <c r="P75">
-        <v>-90.15106815000036</v>
+        <v>-110.5819047000001</v>
       </c>
       <c r="Q75">
-        <v>453.1489318499994</v>
+        <v>432.7180952999996</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1844158004011262</v>
+        <v>0.1897471773396311</v>
       </c>
       <c r="T75">
-        <v>2.77836797071211</v>
+        <v>2.88522827727796</v>
       </c>
       <c r="U75">
         <v>0.1186</v>
       </c>
       <c r="V75">
-        <v>0.23488869831616</v>
+        <v>0.231714526717293</v>
       </c>
       <c r="W75">
-        <v>0.09074220037970343</v>
+        <v>0.09111865713132906</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.93955479326464</v>
+        <v>0.926858106869172</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1167620723854876</v>
+        <v>0.1174900723854876</v>
       </c>
       <c r="C76">
-        <v>-1551.490552024621</v>
+        <v>-1911.467294346437</v>
       </c>
       <c r="D76">
-        <v>15238.39544797538</v>
+        <v>15108.10770565357</v>
       </c>
       <c r="E76">
-        <v>13668.286</v>
+        <v>13897.975</v>
       </c>
       <c r="F76">
-        <v>16996.986</v>
+        <v>17226.675</v>
       </c>
       <c r="G76">
         <v>207.1</v>
@@ -7507,37 +7507,37 @@
         <v>1868.4</v>
       </c>
       <c r="M76">
-        <v>2015.8425396</v>
+        <v>2043.083655000001</v>
       </c>
       <c r="N76">
-        <v>-147.4425396000001</v>
+        <v>-174.6836550000005</v>
       </c>
       <c r="O76">
-        <v>-36.86063490000004</v>
+        <v>-43.67091375000012</v>
       </c>
       <c r="P76">
-        <v>-110.5819047000001</v>
+        <v>-131.0127412500004</v>
       </c>
       <c r="Q76">
-        <v>432.7180952999996</v>
+        <v>412.2872587499994</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1897471773396311</v>
+        <v>0.1955050644332163</v>
       </c>
       <c r="T76">
-        <v>2.88522827727796</v>
+        <v>3.000637408369078</v>
       </c>
       <c r="U76">
         <v>0.1186</v>
       </c>
       <c r="V76">
-        <v>0.231714526717293</v>
+        <v>0.2286249996943957</v>
       </c>
       <c r="W76">
-        <v>0.09111865713132906</v>
+        <v>0.09148507503624467</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.926858106869172</v>
+        <v>0.9144999987775829</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1174900723854876</v>
+        <v>0.1182180723854876</v>
       </c>
       <c r="C77">
-        <v>-1911.467294346437</v>
+        <v>-2269.235012565261</v>
       </c>
       <c r="D77">
-        <v>15108.10770565357</v>
+        <v>14980.02898743474</v>
       </c>
       <c r="E77">
-        <v>13897.975</v>
+        <v>14127.664</v>
       </c>
       <c r="F77">
-        <v>17226.675</v>
+        <v>17456.364</v>
       </c>
       <c r="G77">
         <v>207.1</v>
@@ -7589,37 +7589,37 @@
         <v>1868.4</v>
       </c>
       <c r="M77">
-        <v>2043.083655000001</v>
+        <v>2070.3247704</v>
       </c>
       <c r="N77">
-        <v>-174.6836550000005</v>
+        <v>-201.9247704000004</v>
       </c>
       <c r="O77">
-        <v>-43.67091375000012</v>
+        <v>-50.4811926000001</v>
       </c>
       <c r="P77">
-        <v>-131.0127412500004</v>
+        <v>-151.4435778000003</v>
       </c>
       <c r="Q77">
-        <v>412.2872587499994</v>
+        <v>391.8564221999994</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1955050644332163</v>
+        <v>0.201742775451267</v>
       </c>
       <c r="T77">
-        <v>3.000637408369078</v>
+        <v>3.125663967051124</v>
       </c>
       <c r="U77">
         <v>0.1186</v>
       </c>
       <c r="V77">
-        <v>0.2286249996943957</v>
+        <v>0.2256167760142063</v>
       </c>
       <c r="W77">
-        <v>0.09148507503624467</v>
+        <v>0.09184185036471515</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.9144999987775829</v>
+        <v>0.9024671040568253</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1182180723854876</v>
+        <v>0.1189460723854876</v>
       </c>
       <c r="C78">
-        <v>-2269.235012565261</v>
+        <v>-2624.849415301553</v>
       </c>
       <c r="D78">
-        <v>14980.02898743474</v>
+        <v>14854.10358469845</v>
       </c>
       <c r="E78">
-        <v>14127.664</v>
+        <v>14357.353</v>
       </c>
       <c r="F78">
-        <v>17456.364</v>
+        <v>17686.053</v>
       </c>
       <c r="G78">
         <v>207.1</v>
@@ -7671,37 +7671,37 @@
         <v>1868.4</v>
       </c>
       <c r="M78">
-        <v>2070.3247704</v>
+        <v>2097.5658858</v>
       </c>
       <c r="N78">
-        <v>-201.9247704000004</v>
+        <v>-229.1658858000001</v>
       </c>
       <c r="O78">
-        <v>-50.4811926000001</v>
+        <v>-57.29147145000002</v>
       </c>
       <c r="P78">
-        <v>-151.4435778000003</v>
+        <v>-171.8744143500001</v>
       </c>
       <c r="Q78">
-        <v>391.8564221999994</v>
+        <v>371.4255856499997</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.201742775451267</v>
+        <v>0.2085228961230612</v>
       </c>
       <c r="T78">
-        <v>3.125663967051124</v>
+        <v>3.261562400401172</v>
       </c>
       <c r="U78">
         <v>0.1186</v>
       </c>
       <c r="V78">
-        <v>0.2256167760142063</v>
+        <v>0.2226866880140219</v>
       </c>
       <c r="W78">
-        <v>0.09184185036471515</v>
+        <v>0.092189358801537</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.9024671040568253</v>
+        <v>0.8907467520560874</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1189460723854876</v>
+        <v>0.1196740723854876</v>
       </c>
       <c r="C79">
-        <v>-2624.849415301553</v>
+        <v>-2978.364353595593</v>
       </c>
       <c r="D79">
-        <v>14854.10358469845</v>
+        <v>14730.27764640441</v>
       </c>
       <c r="E79">
-        <v>14357.353</v>
+        <v>14587.042</v>
       </c>
       <c r="F79">
-        <v>17686.053</v>
+        <v>17915.742</v>
       </c>
       <c r="G79">
         <v>207.1</v>
@@ -7753,37 +7753,37 @@
         <v>1868.4</v>
       </c>
       <c r="M79">
-        <v>2097.5658858</v>
+        <v>2124.8070012</v>
       </c>
       <c r="N79">
-        <v>-229.1658858000001</v>
+        <v>-256.4070012000002</v>
       </c>
       <c r="O79">
-        <v>-57.29147145000002</v>
+        <v>-64.10175030000005</v>
       </c>
       <c r="P79">
-        <v>-171.8744143500001</v>
+        <v>-192.3052509000001</v>
       </c>
       <c r="Q79">
-        <v>371.4255856499997</v>
+        <v>350.9947490999996</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2085228961230612</v>
+        <v>0.2159193914013822</v>
       </c>
       <c r="T79">
-        <v>3.261562400401172</v>
+        <v>3.409815236783044</v>
       </c>
       <c r="U79">
         <v>0.1186</v>
       </c>
       <c r="V79">
-        <v>0.2226866880140219</v>
+        <v>0.2198317304753805</v>
       </c>
       <c r="W79">
-        <v>0.092189358801537</v>
+        <v>0.09252795676561988</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8907467520560874</v>
+        <v>0.8793269219015222</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1196740723854876</v>
+        <v>0.1204020723854876</v>
       </c>
       <c r="C80">
-        <v>-2978.364353595593</v>
+        <v>-3329.831897692602</v>
       </c>
       <c r="D80">
-        <v>14730.27764640441</v>
+        <v>14608.4991023074</v>
       </c>
       <c r="E80">
-        <v>14587.042</v>
+        <v>14816.731</v>
       </c>
       <c r="F80">
-        <v>17915.742</v>
+        <v>18145.431</v>
       </c>
       <c r="G80">
         <v>207.1</v>
@@ -7835,37 +7835,37 @@
         <v>1868.4</v>
       </c>
       <c r="M80">
-        <v>2124.8070012</v>
+        <v>2152.0481166</v>
       </c>
       <c r="N80">
-        <v>-256.4070012000002</v>
+        <v>-283.6481166000003</v>
       </c>
       <c r="O80">
-        <v>-64.10175030000005</v>
+        <v>-70.91202915000008</v>
       </c>
       <c r="P80">
-        <v>-192.3052509000001</v>
+        <v>-212.7360874500002</v>
       </c>
       <c r="Q80">
-        <v>350.9947490999996</v>
+        <v>330.5639125499995</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2159193914013822</v>
+        <v>0.224020314801448</v>
       </c>
       <c r="T80">
-        <v>3.409815236783044</v>
+        <v>3.572187390915571</v>
       </c>
       <c r="U80">
         <v>0.1186</v>
       </c>
       <c r="V80">
-        <v>0.2198317304753805</v>
+        <v>0.2170490503427808</v>
       </c>
       <c r="W80">
-        <v>0.09252795676561988</v>
+        <v>0.09285798262934621</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8793269219015222</v>
+        <v>0.8681962013711231</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1204020723854876</v>
+        <v>0.1211300723854876</v>
       </c>
       <c r="C81">
-        <v>-3329.831897692602</v>
+        <v>-3679.302410050421</v>
       </c>
       <c r="D81">
-        <v>14608.4991023074</v>
+        <v>14488.71758994958</v>
       </c>
       <c r="E81">
-        <v>14816.731</v>
+        <v>15046.42</v>
       </c>
       <c r="F81">
-        <v>18145.431</v>
+        <v>18375.12</v>
       </c>
       <c r="G81">
         <v>207.1</v>
@@ -7917,37 +7917,37 @@
         <v>1868.4</v>
       </c>
       <c r="M81">
-        <v>2152.0481166</v>
+        <v>2179.289232000001</v>
       </c>
       <c r="N81">
-        <v>-283.6481166000003</v>
+        <v>-310.8892320000004</v>
       </c>
       <c r="O81">
-        <v>-70.91202915000008</v>
+        <v>-77.72230800000011</v>
       </c>
       <c r="P81">
-        <v>-212.7360874500002</v>
+        <v>-233.1669240000003</v>
       </c>
       <c r="Q81">
-        <v>330.5639125499995</v>
+        <v>310.1330759999994</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.224020314801448</v>
+        <v>0.2329313305415204</v>
       </c>
       <c r="T81">
-        <v>3.572187390915571</v>
+        <v>3.750796760461349</v>
       </c>
       <c r="U81">
         <v>0.1186</v>
       </c>
       <c r="V81">
-        <v>0.2170490503427808</v>
+        <v>0.214335937213496</v>
       </c>
       <c r="W81">
-        <v>0.09285798262934621</v>
+        <v>0.09317975784647939</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8681962013711231</v>
+        <v>0.857343748853984</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1211300723854876</v>
+        <v>0.1218580723854876</v>
       </c>
       <c r="C82">
-        <v>-3679.302410050421</v>
+        <v>-4026.824614784538</v>
       </c>
       <c r="D82">
-        <v>14488.71758994958</v>
+        <v>14370.88438521546</v>
       </c>
       <c r="E82">
-        <v>15046.42</v>
+        <v>15276.109</v>
       </c>
       <c r="F82">
-        <v>18375.12</v>
+        <v>18604.809</v>
       </c>
       <c r="G82">
         <v>207.1</v>
@@ -7999,37 +7999,37 @@
         <v>1868.4</v>
       </c>
       <c r="M82">
-        <v>2179.289232000001</v>
+        <v>2206.5303474</v>
       </c>
       <c r="N82">
-        <v>-310.8892320000004</v>
+        <v>-338.1303474000001</v>
       </c>
       <c r="O82">
-        <v>-77.72230800000011</v>
+        <v>-84.53258685000003</v>
       </c>
       <c r="P82">
-        <v>-233.1669240000003</v>
+        <v>-253.5977605500001</v>
       </c>
       <c r="Q82">
-        <v>310.1330759999994</v>
+        <v>289.7022394499996</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2329313305415204</v>
+        <v>0.2427803479384426</v>
       </c>
       <c r="T82">
-        <v>3.750796760461349</v>
+        <v>3.948207116275104</v>
       </c>
       <c r="U82">
         <v>0.1186</v>
       </c>
       <c r="V82">
-        <v>0.214335937213496</v>
+        <v>0.2116898145318479</v>
       </c>
       <c r="W82">
-        <v>0.09317975784647939</v>
+        <v>0.09349358799652284</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.857343748853984</v>
+        <v>0.8467592581273917</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1218580723854876</v>
+        <v>0.1225860723854876</v>
       </c>
       <c r="C83">
-        <v>-4026.824614784538</v>
+        <v>-4372.445663751898</v>
       </c>
       <c r="D83">
-        <v>14370.88438521546</v>
+        <v>14254.9523362481</v>
       </c>
       <c r="E83">
-        <v>15276.109</v>
+        <v>15505.798</v>
       </c>
       <c r="F83">
-        <v>18604.809</v>
+        <v>18834.498</v>
       </c>
       <c r="G83">
         <v>207.1</v>
@@ -8081,37 +8081,37 @@
         <v>1868.4</v>
       </c>
       <c r="M83">
-        <v>2206.5303474</v>
+        <v>2233.771462800001</v>
       </c>
       <c r="N83">
-        <v>-338.1303474000001</v>
+        <v>-365.3714628000007</v>
       </c>
       <c r="O83">
-        <v>-84.53258685000003</v>
+        <v>-91.34286570000017</v>
       </c>
       <c r="P83">
-        <v>-253.5977605500001</v>
+        <v>-274.0285971000005</v>
       </c>
       <c r="Q83">
-        <v>289.7022394499996</v>
+        <v>269.2714028999992</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2427803479384426</v>
+        <v>0.2537237006016894</v>
       </c>
       <c r="T83">
-        <v>3.948207116275104</v>
+        <v>4.167551956068166</v>
       </c>
       <c r="U83">
         <v>0.1186</v>
       </c>
       <c r="V83">
-        <v>0.2116898145318479</v>
+        <v>0.2091082314278009</v>
       </c>
       <c r="W83">
-        <v>0.09349358799652284</v>
+        <v>0.09379976375266282</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8467592581273917</v>
+        <v>0.8364329257112038</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1225860723854876</v>
+        <v>0.1233140723854876</v>
       </c>
       <c r="C84">
-        <v>-4372.445663751898</v>
+        <v>-4716.211199461555</v>
       </c>
       <c r="D84">
-        <v>14254.9523362481</v>
+        <v>14140.87580053845</v>
       </c>
       <c r="E84">
-        <v>15505.798</v>
+        <v>15735.487</v>
       </c>
       <c r="F84">
-        <v>18834.498</v>
+        <v>19064.187</v>
       </c>
       <c r="G84">
         <v>207.1</v>
@@ -8163,37 +8163,37 @@
         <v>1868.4</v>
       </c>
       <c r="M84">
-        <v>2233.771462800001</v>
+        <v>2261.0125782</v>
       </c>
       <c r="N84">
-        <v>-365.3714628000007</v>
+        <v>-392.6125782000004</v>
       </c>
       <c r="O84">
-        <v>-91.34286570000017</v>
+        <v>-98.15314455000009</v>
       </c>
       <c r="P84">
-        <v>-274.0285971000005</v>
+        <v>-294.4594336500003</v>
       </c>
       <c r="Q84">
-        <v>269.2714028999992</v>
+        <v>248.8405663499994</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2537237006016894</v>
+        <v>0.2659545065194359</v>
       </c>
       <c r="T84">
-        <v>4.167551956068166</v>
+        <v>4.412702071131</v>
       </c>
       <c r="U84">
         <v>0.1186</v>
       </c>
       <c r="V84">
-        <v>0.2091082314278009</v>
+        <v>0.2065888551455383</v>
       </c>
       <c r="W84">
-        <v>0.09379976375266282</v>
+        <v>0.09409856177973916</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8364329257112038</v>
+        <v>0.8263554205821533</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1233140723854876</v>
+        <v>0.1240420723854876</v>
       </c>
       <c r="C85">
-        <v>-4716.211199461555</v>
+        <v>-5058.165414988687</v>
       </c>
       <c r="D85">
-        <v>14140.87580053845</v>
+        <v>14028.61058501132</v>
       </c>
       <c r="E85">
-        <v>15735.487</v>
+        <v>15965.176</v>
       </c>
       <c r="F85">
-        <v>19064.187</v>
+        <v>19293.876</v>
       </c>
       <c r="G85">
         <v>207.1</v>
@@ -8245,37 +8245,37 @@
         <v>1868.4</v>
       </c>
       <c r="M85">
-        <v>2261.0125782</v>
+        <v>2288.253693600001</v>
       </c>
       <c r="N85">
-        <v>-392.6125782000004</v>
+        <v>-419.8536936000005</v>
       </c>
       <c r="O85">
-        <v>-98.15314455000009</v>
+        <v>-104.9634234000001</v>
       </c>
       <c r="P85">
-        <v>-294.4594336500003</v>
+        <v>-314.8902702000004</v>
       </c>
       <c r="Q85">
-        <v>248.8405663499994</v>
+        <v>228.4097297999994</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2659545065194359</v>
+        <v>0.2797141631769006</v>
       </c>
       <c r="T85">
-        <v>4.412702071131</v>
+        <v>4.688495950576688</v>
       </c>
       <c r="U85">
         <v>0.1186</v>
       </c>
       <c r="V85">
-        <v>0.2065888551455383</v>
+        <v>0.2041294640128533</v>
       </c>
       <c r="W85">
-        <v>0.09409856177973916</v>
+        <v>0.0943902455680756</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8263554205821533</v>
+        <v>0.8165178560514132</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1240420723854876</v>
+        <v>0.1247700723854876</v>
       </c>
       <c r="C86">
-        <v>-5058.165414988684</v>
+        <v>-5398.351111057105</v>
       </c>
       <c r="D86">
-        <v>14028.61058501132</v>
+        <v>13918.1138889429</v>
       </c>
       <c r="E86">
-        <v>15965.176</v>
+        <v>16194.865</v>
       </c>
       <c r="F86">
-        <v>19293.876</v>
+        <v>19523.565</v>
       </c>
       <c r="G86">
         <v>207.1</v>
@@ -8327,37 +8327,37 @@
         <v>1868.4</v>
       </c>
       <c r="M86">
-        <v>2288.2536936</v>
+        <v>2315.494809000001</v>
       </c>
       <c r="N86">
-        <v>-419.8536936</v>
+        <v>-447.0948090000006</v>
       </c>
       <c r="O86">
-        <v>-104.9634234</v>
+        <v>-111.7737022500002</v>
       </c>
       <c r="P86">
-        <v>-314.8902702</v>
+        <v>-335.3211067500005</v>
       </c>
       <c r="Q86">
-        <v>228.4097297999997</v>
+        <v>207.9788932499993</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2797141631769005</v>
+        <v>0.2953084407220272</v>
       </c>
       <c r="T86">
-        <v>4.688495950576685</v>
+        <v>5.001062347281797</v>
       </c>
       <c r="U86">
         <v>0.1186</v>
       </c>
       <c r="V86">
-        <v>0.2041294640128534</v>
+        <v>0.2017279409068198</v>
       </c>
       <c r="W86">
-        <v>0.0943902455680756</v>
+        <v>0.09467506620845119</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8165178560514135</v>
+        <v>0.806911763627279</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1247700723854876</v>
+        <v>0.1993608128709803</v>
       </c>
       <c r="C87">
-        <v>-5398.351111057105</v>
+        <v>-11843.93795246262</v>
       </c>
       <c r="D87">
-        <v>13918.1138889429</v>
+        <v>7702.216047537379</v>
       </c>
       <c r="E87">
-        <v>16194.865</v>
+        <v>16424.554</v>
       </c>
       <c r="F87">
-        <v>19523.565</v>
+        <v>19753.254</v>
       </c>
       <c r="G87">
         <v>207.1</v>
@@ -8409,45 +8409,45 @@
         <v>1868.4</v>
       </c>
       <c r="M87">
-        <v>2315.494809000001</v>
+        <v>3966.4534032</v>
       </c>
       <c r="N87">
-        <v>-447.0948090000006</v>
+        <v>-2098.0534032</v>
       </c>
       <c r="O87">
-        <v>-111.7737022500002</v>
+        <v>-524.5133508</v>
       </c>
       <c r="P87">
-        <v>-335.3211067500005</v>
+        <v>-1573.5400524</v>
       </c>
       <c r="Q87">
-        <v>207.9788932499993</v>
+        <v>-1030.2400524</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2953084407220272</v>
+        <v>0.3357786185271198</v>
       </c>
       <c r="T87">
-        <v>5.001062347281797</v>
+        <v>5.812232830425216</v>
       </c>
       <c r="U87">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.2017279409068198</v>
+        <v>0.1177626338993821</v>
       </c>
       <c r="W87">
-        <v>0.09467506620845119</v>
+        <v>0.1771532631130041</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.806911763627279</v>
+        <v>0.4710505355975286</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1993608128709803</v>
+        <v>0.2009108128709803</v>
       </c>
       <c r="C88">
-        <v>-11843.93795246262</v>
+        <v>-12144.44991446193</v>
       </c>
       <c r="D88">
-        <v>7702.216047537379</v>
+        <v>7631.393085538078</v>
       </c>
       <c r="E88">
-        <v>16424.554</v>
+        <v>16654.243</v>
       </c>
       <c r="F88">
-        <v>19753.254</v>
+        <v>19982.943</v>
       </c>
       <c r="G88">
         <v>207.1</v>
@@ -8491,37 +8491,37 @@
         <v>1868.4</v>
       </c>
       <c r="M88">
-        <v>3966.4534032</v>
+        <v>4012.574954400001</v>
       </c>
       <c r="N88">
-        <v>-2098.0534032</v>
+        <v>-2144.174954400001</v>
       </c>
       <c r="O88">
-        <v>-524.5133508</v>
+        <v>-536.0437386000002</v>
       </c>
       <c r="P88">
-        <v>-1573.5400524</v>
+        <v>-1608.131215800001</v>
       </c>
       <c r="Q88">
-        <v>-1030.2400524</v>
+        <v>-1064.831215800001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3357786185271198</v>
+        <v>0.358084666106129</v>
       </c>
       <c r="T88">
-        <v>5.812232830425216</v>
+        <v>6.259327663534848</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1177626338993821</v>
+        <v>0.1164090404062858</v>
       </c>
       <c r="W88">
-        <v>0.1771532631130041</v>
+        <v>0.1774250646864178</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4710505355975286</v>
+        <v>0.4656361616251431</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2009108128709803</v>
+        <v>0.2024608128709803</v>
       </c>
       <c r="C89">
-        <v>-12144.44991446193</v>
+        <v>-12443.67128935875</v>
       </c>
       <c r="D89">
-        <v>7631.393085538078</v>
+        <v>7561.860710641247</v>
       </c>
       <c r="E89">
-        <v>16654.243</v>
+        <v>16883.932</v>
       </c>
       <c r="F89">
-        <v>19982.943</v>
+        <v>20212.632</v>
       </c>
       <c r="G89">
         <v>207.1</v>
@@ -8573,37 +8573,37 @@
         <v>1868.4</v>
       </c>
       <c r="M89">
-        <v>4012.574954400001</v>
+        <v>4058.6965056</v>
       </c>
       <c r="N89">
-        <v>-2144.174954400001</v>
+        <v>-2190.2965056</v>
       </c>
       <c r="O89">
-        <v>-536.0437386000002</v>
+        <v>-547.5741264000001</v>
       </c>
       <c r="P89">
-        <v>-1608.131215800001</v>
+        <v>-1642.7223792</v>
       </c>
       <c r="Q89">
-        <v>-1064.831215800001</v>
+        <v>-1099.4223792</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.358084666106129</v>
+        <v>0.3841083882816398</v>
       </c>
       <c r="T89">
-        <v>6.259327663534848</v>
+        <v>6.780938302162753</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1164090404062858</v>
+        <v>0.1150862104016689</v>
       </c>
       <c r="W89">
-        <v>0.1774250646864178</v>
+        <v>0.1776906889513449</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4656361616251431</v>
+        <v>0.4603448416066757</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2024608128709803</v>
+        <v>0.2040108128709803</v>
       </c>
       <c r="C90">
-        <v>-12443.67128935875</v>
+        <v>-12741.6370356474</v>
       </c>
       <c r="D90">
-        <v>7561.860710641247</v>
+        <v>7493.5839643526</v>
       </c>
       <c r="E90">
-        <v>16883.932</v>
+        <v>17113.621</v>
       </c>
       <c r="F90">
-        <v>20212.632</v>
+        <v>20442.321</v>
       </c>
       <c r="G90">
         <v>207.1</v>
@@ -8655,37 +8655,37 @@
         <v>1868.4</v>
       </c>
       <c r="M90">
-        <v>4058.6965056</v>
+        <v>4104.8180568</v>
       </c>
       <c r="N90">
-        <v>-2190.2965056</v>
+        <v>-2236.4180568</v>
       </c>
       <c r="O90">
-        <v>-547.5741264000001</v>
+        <v>-559.1045141999999</v>
       </c>
       <c r="P90">
-        <v>-1642.7223792</v>
+        <v>-1677.3135426</v>
       </c>
       <c r="Q90">
-        <v>-1099.4223792</v>
+        <v>-1134.0135426</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3841083882816398</v>
+        <v>0.4148636963072433</v>
       </c>
       <c r="T90">
-        <v>6.780938302162753</v>
+        <v>7.397387238723003</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1150862104016689</v>
+        <v>0.1137931069140097</v>
       </c>
       <c r="W90">
-        <v>0.1776906889513449</v>
+        <v>0.1779503441316669</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4603448416066757</v>
+        <v>0.4551724276560389</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2040108128709803</v>
+        <v>0.2055608128709802</v>
       </c>
       <c r="C91">
-        <v>-12741.6370356474</v>
+        <v>-13038.38086054602</v>
       </c>
       <c r="D91">
-        <v>7493.5839643526</v>
+        <v>7426.529139453985</v>
       </c>
       <c r="E91">
-        <v>17113.621</v>
+        <v>17343.31</v>
       </c>
       <c r="F91">
-        <v>20442.321</v>
+        <v>20672.01</v>
       </c>
       <c r="G91">
         <v>207.1</v>
@@ -8737,37 +8737,37 @@
         <v>1868.4</v>
       </c>
       <c r="M91">
-        <v>4104.8180568</v>
+        <v>4150.939608000001</v>
       </c>
       <c r="N91">
-        <v>-2236.4180568</v>
+        <v>-2282.539608</v>
       </c>
       <c r="O91">
-        <v>-559.1045141999999</v>
+        <v>-570.6349020000001</v>
       </c>
       <c r="P91">
-        <v>-1677.3135426</v>
+        <v>-1711.904706</v>
       </c>
       <c r="Q91">
-        <v>-1134.0135426</v>
+        <v>-1168.604706000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4148636963072433</v>
+        <v>0.4517700659379677</v>
       </c>
       <c r="T91">
-        <v>7.397387238723003</v>
+        <v>8.137125962595304</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1137931069140097</v>
+        <v>0.1125287390594096</v>
       </c>
       <c r="W91">
-        <v>0.1779503441316669</v>
+        <v>0.1782042291968705</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4551724276560389</v>
+        <v>0.4501149562376384</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2055608128709802</v>
+        <v>0.2071108128709803</v>
       </c>
       <c r="C92">
-        <v>-13038.38086054602</v>
+        <v>-13333.93527548404</v>
       </c>
       <c r="D92">
-        <v>7426.529139453985</v>
+        <v>7360.66372451596</v>
       </c>
       <c r="E92">
-        <v>17343.31</v>
+        <v>17572.999</v>
       </c>
       <c r="F92">
-        <v>20672.01</v>
+        <v>20901.699</v>
       </c>
       <c r="G92">
         <v>207.1</v>
@@ -8819,37 +8819,37 @@
         <v>1868.4</v>
       </c>
       <c r="M92">
-        <v>4150.939608000001</v>
+        <v>4197.0611592</v>
       </c>
       <c r="N92">
-        <v>-2282.539608</v>
+        <v>-2328.6611592</v>
       </c>
       <c r="O92">
-        <v>-570.6349020000001</v>
+        <v>-582.1652898000001</v>
       </c>
       <c r="P92">
-        <v>-1711.904706</v>
+        <v>-1746.4958694</v>
       </c>
       <c r="Q92">
-        <v>-1168.604706000001</v>
+        <v>-1203.1958694</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4517700659379677</v>
+        <v>0.4968778510421865</v>
       </c>
       <c r="T92">
-        <v>8.137125962595304</v>
+        <v>9.04125106955034</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1125287390594096</v>
+        <v>0.1112921595093062</v>
       </c>
       <c r="W92">
-        <v>0.1782042291968705</v>
+        <v>0.1784525343705313</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4501149562376384</v>
+        <v>0.4451686380372248</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2071108128709803</v>
+        <v>0.2086608128709803</v>
       </c>
       <c r="C93">
-        <v>-13333.93527548404</v>
+        <v>-13628.33164866293</v>
       </c>
       <c r="D93">
-        <v>7360.66372451596</v>
+        <v>7295.956351337075</v>
       </c>
       <c r="E93">
-        <v>17572.999</v>
+        <v>17802.688</v>
       </c>
       <c r="F93">
-        <v>20901.699</v>
+        <v>21131.388</v>
       </c>
       <c r="G93">
         <v>207.1</v>
@@ -8901,37 +8901,37 @@
         <v>1868.4</v>
       </c>
       <c r="M93">
-        <v>4197.0611592</v>
+        <v>4243.1827104</v>
       </c>
       <c r="N93">
-        <v>-2328.6611592</v>
+        <v>-2374.7827104</v>
       </c>
       <c r="O93">
-        <v>-582.1652898000001</v>
+        <v>-593.6956776000001</v>
       </c>
       <c r="P93">
-        <v>-1746.4958694</v>
+        <v>-1781.0870328</v>
       </c>
       <c r="Q93">
-        <v>-1203.1958694</v>
+        <v>-1237.7870328</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4968778510421865</v>
+        <v>0.5532625824224597</v>
       </c>
       <c r="T93">
-        <v>9.04125106955034</v>
+        <v>10.17140745324413</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1112921595093062</v>
+        <v>0.1100824621233355</v>
       </c>
       <c r="W93">
-        <v>0.1784525343705313</v>
+        <v>0.1786954416056342</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4451686380372248</v>
+        <v>0.4403298484933419</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2086608128709803</v>
+        <v>0.2102108128709803</v>
       </c>
       <c r="C94">
-        <v>-13628.33164866293</v>
+        <v>-13921.60025486866</v>
       </c>
       <c r="D94">
-        <v>7295.956351337075</v>
+        <v>7232.376745131345</v>
       </c>
       <c r="E94">
-        <v>17802.688</v>
+        <v>18032.377</v>
       </c>
       <c r="F94">
-        <v>21131.388</v>
+        <v>21361.077</v>
       </c>
       <c r="G94">
         <v>207.1</v>
@@ -8983,37 +8983,37 @@
         <v>1868.4</v>
       </c>
       <c r="M94">
-        <v>4243.1827104</v>
+        <v>4289.3042616</v>
       </c>
       <c r="N94">
-        <v>-2374.7827104</v>
+        <v>-2420.9042616</v>
       </c>
       <c r="O94">
-        <v>-593.6956776000001</v>
+        <v>-605.2260654</v>
       </c>
       <c r="P94">
-        <v>-1781.0870328</v>
+        <v>-1815.6781962</v>
       </c>
       <c r="Q94">
-        <v>-1237.7870328</v>
+        <v>-1272.3781962</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5532625824224597</v>
+        <v>0.6257572370542399</v>
       </c>
       <c r="T94">
-        <v>10.17140745324413</v>
+        <v>11.62446566085044</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1100824621233355</v>
+        <v>0.1088987797349125</v>
       </c>
       <c r="W94">
-        <v>0.1786954416056342</v>
+        <v>0.1789331250292296</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4403298484933419</v>
+        <v>0.4355951189396501</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2102108128709803</v>
+        <v>0.2117608128709803</v>
       </c>
       <c r="C95">
-        <v>-13921.60025486866</v>
+        <v>-14213.77032270224</v>
       </c>
       <c r="D95">
-        <v>7232.376745131345</v>
+        <v>7169.895677297761</v>
       </c>
       <c r="E95">
-        <v>18032.377</v>
+        <v>18262.066</v>
       </c>
       <c r="F95">
-        <v>21361.077</v>
+        <v>21590.766</v>
       </c>
       <c r="G95">
         <v>207.1</v>
@@ -9065,37 +9065,37 @@
         <v>1868.4</v>
       </c>
       <c r="M95">
-        <v>4289.3042616</v>
+        <v>4335.425812800001</v>
       </c>
       <c r="N95">
-        <v>-2420.9042616</v>
+        <v>-2467.025812800001</v>
       </c>
       <c r="O95">
-        <v>-605.2260654</v>
+        <v>-616.7564532000002</v>
       </c>
       <c r="P95">
-        <v>-1815.6781962</v>
+        <v>-1850.269359600001</v>
       </c>
       <c r="Q95">
-        <v>-1272.3781962</v>
+        <v>-1306.969359600001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6257572370542399</v>
+        <v>0.7224167765632801</v>
       </c>
       <c r="T95">
-        <v>11.62446566085044</v>
+        <v>13.56187660432552</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1088987797349125</v>
+        <v>0.1077402820781581</v>
       </c>
       <c r="W95">
-        <v>0.1789331250292296</v>
+        <v>0.1791657513587059</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4355951189396501</v>
+        <v>0.4309611283126324</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2117608128709803</v>
+        <v>0.2133108128709803</v>
       </c>
       <c r="C96">
-        <v>-14213.77032270224</v>
+        <v>-14504.87007938303</v>
       </c>
       <c r="D96">
-        <v>7169.895677297761</v>
+        <v>7108.484920616972</v>
       </c>
       <c r="E96">
-        <v>18262.066</v>
+        <v>18491.755</v>
       </c>
       <c r="F96">
-        <v>21590.766</v>
+        <v>21820.455</v>
       </c>
       <c r="G96">
         <v>207.1</v>
@@ -9147,37 +9147,37 @@
         <v>1868.4</v>
       </c>
       <c r="M96">
-        <v>4335.425812800001</v>
+        <v>4381.547364000001</v>
       </c>
       <c r="N96">
-        <v>-2467.025812800001</v>
+        <v>-2513.147364000001</v>
       </c>
       <c r="O96">
-        <v>-616.7564532000002</v>
+        <v>-628.2868410000002</v>
       </c>
       <c r="P96">
-        <v>-1850.269359600001</v>
+        <v>-1884.860523000001</v>
       </c>
       <c r="Q96">
-        <v>-1306.969359600001</v>
+        <v>-1341.560523000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7224167765632801</v>
+        <v>0.8577401318759366</v>
       </c>
       <c r="T96">
-        <v>13.56187660432552</v>
+        <v>16.27425192519063</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1077402820781581</v>
+        <v>0.1066061738457564</v>
       </c>
       <c r="W96">
-        <v>0.1791657513587059</v>
+        <v>0.1793934802917721</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4309611283126324</v>
+        <v>0.4264246953830259</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2133108128709803</v>
+        <v>0.2148608128709803</v>
       </c>
       <c r="C97">
-        <v>-14504.87007938303</v>
+        <v>-14794.92679326912</v>
       </c>
       <c r="D97">
-        <v>7108.484920616972</v>
+        <v>7048.11720673088</v>
       </c>
       <c r="E97">
-        <v>18491.755</v>
+        <v>18721.444</v>
       </c>
       <c r="F97">
-        <v>21820.455</v>
+        <v>22050.144</v>
       </c>
       <c r="G97">
         <v>207.1</v>
@@ -9229,37 +9229,37 @@
         <v>1868.4</v>
       </c>
       <c r="M97">
-        <v>4381.547364000001</v>
+        <v>4427.668915200001</v>
       </c>
       <c r="N97">
-        <v>-2513.147364000001</v>
+        <v>-2559.268915200001</v>
       </c>
       <c r="O97">
-        <v>-628.2868410000002</v>
+        <v>-639.8172288000002</v>
       </c>
       <c r="P97">
-        <v>-1884.860523000001</v>
+        <v>-1919.451686400001</v>
       </c>
       <c r="Q97">
-        <v>-1341.560523000001</v>
+        <v>-1376.151686400001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8577401318759366</v>
+        <v>1.060725164844921</v>
       </c>
       <c r="T97">
-        <v>16.27425192519063</v>
+        <v>20.3428149064883</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1066061738457564</v>
+        <v>0.1054956928681965</v>
       </c>
       <c r="W97">
-        <v>0.1793934802917721</v>
+        <v>0.1796164648720661</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4264246953830259</v>
+        <v>0.421982771472786</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2148608128709803</v>
+        <v>0.2164108128709803</v>
       </c>
       <c r="C98">
-        <v>-14794.92679326912</v>
+        <v>-15083.96681422941</v>
       </c>
       <c r="D98">
-        <v>7048.11720673088</v>
+        <v>6988.766185770596</v>
       </c>
       <c r="E98">
-        <v>18721.444</v>
+        <v>18951.133</v>
       </c>
       <c r="F98">
-        <v>22050.144</v>
+        <v>22279.833</v>
       </c>
       <c r="G98">
         <v>207.1</v>
@@ -9311,37 +9311,37 @@
         <v>1868.4</v>
       </c>
       <c r="M98">
-        <v>4427.6689152</v>
+        <v>4473.790466400001</v>
       </c>
       <c r="N98">
-        <v>-2559.2689152</v>
+        <v>-2605.390466400001</v>
       </c>
       <c r="O98">
-        <v>-639.8172288</v>
+        <v>-651.3476166000002</v>
       </c>
       <c r="P98">
-        <v>-1919.4516864</v>
+        <v>-1954.042849800001</v>
       </c>
       <c r="Q98">
-        <v>-1376.1516864</v>
+        <v>-1410.742849800001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.060725164844919</v>
+        <v>1.399033553126558</v>
       </c>
       <c r="T98">
-        <v>20.34281490648824</v>
+        <v>27.12375320865099</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1054956928681965</v>
+        <v>0.1044081084056378</v>
       </c>
       <c r="W98">
-        <v>0.1796164648720661</v>
+        <v>0.179834851832148</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4219827714727861</v>
+        <v>0.4176324336225511</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2164108128709803</v>
+        <v>0.2179608128709803</v>
       </c>
       <c r="C99">
-        <v>-15083.96681422941</v>
+        <v>-15372.01561199285</v>
       </c>
       <c r="D99">
-        <v>6988.766185770596</v>
+        <v>6930.406388007149</v>
       </c>
       <c r="E99">
-        <v>18951.133</v>
+        <v>19180.822</v>
       </c>
       <c r="F99">
-        <v>22279.833</v>
+        <v>22509.522</v>
       </c>
       <c r="G99">
         <v>207.1</v>
@@ -9393,37 +9393,37 @@
         <v>1868.4</v>
       </c>
       <c r="M99">
-        <v>4473.790466400001</v>
+        <v>4519.912017600001</v>
       </c>
       <c r="N99">
-        <v>-2605.390466400001</v>
+        <v>-2651.5120176</v>
       </c>
       <c r="O99">
-        <v>-651.3476166000002</v>
+        <v>-662.8780044000001</v>
       </c>
       <c r="P99">
-        <v>-1954.042849800001</v>
+        <v>-1988.6340132</v>
       </c>
       <c r="Q99">
-        <v>-1410.742849800001</v>
+        <v>-1445.334013200001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.399033553126558</v>
+        <v>2.075650329689837</v>
       </c>
       <c r="T99">
-        <v>27.12375320865099</v>
+        <v>40.68562981297649</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1044081084056378</v>
+        <v>0.1033427195443558</v>
       </c>
       <c r="W99">
-        <v>0.179834851832148</v>
+        <v>0.1800487819154934</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4176324336225511</v>
+        <v>0.413370878177423</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2179608128709803</v>
+        <v>0.2195108128709803</v>
       </c>
       <c r="C100">
-        <v>-15372.01561199285</v>
+        <v>-15659.09781259231</v>
       </c>
       <c r="D100">
-        <v>6930.406388007149</v>
+        <v>6873.013187407693</v>
       </c>
       <c r="E100">
-        <v>19180.822</v>
+        <v>19410.511</v>
       </c>
       <c r="F100">
-        <v>22509.522</v>
+        <v>22739.211</v>
       </c>
       <c r="G100">
         <v>207.1</v>
@@ -9475,37 +9475,37 @@
         <v>1868.4</v>
       </c>
       <c r="M100">
-        <v>4519.912017600001</v>
+        <v>4566.0335688</v>
       </c>
       <c r="N100">
-        <v>-2651.5120176</v>
+        <v>-2697.6335688</v>
       </c>
       <c r="O100">
-        <v>-662.8780044000001</v>
+        <v>-674.4083922000001</v>
       </c>
       <c r="P100">
-        <v>-1988.6340132</v>
+        <v>-2023.2251766</v>
       </c>
       <c r="Q100">
-        <v>-1445.334013200001</v>
+        <v>-1479.925176600001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.075650329689837</v>
+        <v>4.105500659379673</v>
       </c>
       <c r="T100">
-        <v>40.68562981297649</v>
+        <v>81.37125962595296</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1033427195443558</v>
+        <v>0.1022988536903724</v>
       </c>
       <c r="W100">
-        <v>0.1800487819154934</v>
+        <v>0.1802583901789732</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.413370878177423</v>
+        <v>0.4091954147614895</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2195108128709803</v>
-      </c>
-      <c r="C101">
-        <v>-15659.09781259231</v>
-      </c>
-      <c r="D101">
-        <v>6873.013187407693</v>
-      </c>
-      <c r="E101">
-        <v>19410.511</v>
-      </c>
-      <c r="F101">
-        <v>22739.211</v>
-      </c>
-      <c r="G101">
-        <v>207.1</v>
-      </c>
-      <c r="H101">
-        <v>19640.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2411.7</v>
-      </c>
-      <c r="K101">
-        <v>543.2999999999997</v>
-      </c>
-      <c r="L101">
-        <v>1868.4</v>
-      </c>
-      <c r="M101">
-        <v>4566.0335688</v>
-      </c>
-      <c r="N101">
-        <v>-2697.6335688</v>
-      </c>
-      <c r="O101">
-        <v>-674.4083922000001</v>
-      </c>
-      <c r="P101">
-        <v>-2023.2251766</v>
-      </c>
-      <c r="Q101">
-        <v>-1479.925176600001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.105500659379673</v>
-      </c>
-      <c r="T101">
-        <v>81.37125962595296</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1022988536903724</v>
-      </c>
-      <c r="W101">
-        <v>0.1802583901789732</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4091954147614895</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
